--- a/database/event/4205/event_4205_evp_summary.xlsx
+++ b/database/event/4205/event_4205_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.9763</v>
+        <v>7.2347</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0462</v>
+        <v>2.4771</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9929</v>
+        <v>2.4384</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9763</v>
+        <v>7.2347</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8245</v>
+        <v>5.0829</v>
       </c>
       <c r="G2" t="n">
         <v>2.1518</v>
       </c>
       <c r="H2" t="n">
-        <v>3.8245</v>
+        <v>5.6669</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8602</v>
+        <v>5.7627</v>
       </c>
       <c r="J2" t="n">
         <v>2.1518</v>
@@ -529,7 +529,7 @@
         <v>68</v>
       </c>
       <c r="M2" t="n">
-        <v>6.012</v>
+        <v>7.9145</v>
       </c>
       <c r="N2" t="n">
         <v>193</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7317</v>
+        <v>6.8081</v>
       </c>
       <c r="C3" t="n">
-        <v>1.9625</v>
+        <v>2.331</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8941</v>
+        <v>2.2684</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7317</v>
+        <v>6.8081</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6687</v>
+        <v>4.7451</v>
       </c>
       <c r="G3" t="n">
         <v>2.063</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6687</v>
+        <v>5.1373</v>
       </c>
       <c r="I3" t="n">
-        <v>3.7029</v>
+        <v>5.2241</v>
       </c>
       <c r="J3" t="n">
         <v>2.063</v>
@@ -575,7 +575,7 @@
         <v>68</v>
       </c>
       <c r="M3" t="n">
-        <v>5.7659</v>
+        <v>7.287100000000001</v>
       </c>
       <c r="N3" t="n">
         <v>193</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.0636</v>
+        <v>4.1714</v>
       </c>
       <c r="C4" t="n">
-        <v>1.0489</v>
+        <v>1.4282</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8163</v>
+        <v>1.218</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0636</v>
+        <v>4.1714</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2255</v>
+        <v>3.3333</v>
       </c>
       <c r="G4" t="n">
         <v>0.8381</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2255</v>
+        <v>3.3333</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2255</v>
+        <v>3.3333</v>
       </c>
       <c r="J4" t="n">
         <v>0.8381</v>
@@ -621,7 +621,7 @@
         <v>68</v>
       </c>
       <c r="M4" t="n">
-        <v>3.0636</v>
+        <v>4.1714</v>
       </c>
       <c r="N4" t="n">
         <v>194</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.2638</v>
+        <v>3.4502</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7751</v>
+        <v>1.1813</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4932</v>
+        <v>0.9306</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2638</v>
+        <v>3.4502</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2638</v>
+        <v>3.4502</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2638</v>
+        <v>3.4502</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2638</v>
+        <v>3.4502</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.2638</v>
+        <v>3.4502</v>
       </c>
       <c r="N5" t="n">
         <v>123</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.0887</v>
+        <v>2.6458</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7151</v>
+        <v>0.9059</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4224</v>
+        <v>0.6102</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0887</v>
+        <v>2.6458</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0064</v>
+        <v>1.5635</v>
       </c>
       <c r="G6" t="n">
         <v>1.0823</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0064</v>
+        <v>1.5635</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0158</v>
+        <v>1.5899</v>
       </c>
       <c r="J6" t="n">
         <v>1.0823</v>
@@ -713,7 +713,7 @@
         <v>68</v>
       </c>
       <c r="M6" t="n">
-        <v>2.0981</v>
+        <v>2.6722</v>
       </c>
       <c r="N6" t="n">
         <v>193</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.7187</v>
+        <v>2.2368</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5885</v>
+        <v>0.7659</v>
       </c>
       <c r="D7" t="n">
-        <v>0.273</v>
+        <v>0.4472</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7187</v>
+        <v>2.2368</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8786</v>
+        <v>2.3967</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1599</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8786</v>
+        <v>2.3967</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8786</v>
+        <v>2.3967</v>
       </c>
       <c r="J7" t="n">
         <v>-0.1599</v>
@@ -759,7 +759,7 @@
         <v>68</v>
       </c>
       <c r="M7" t="n">
-        <v>1.7187</v>
+        <v>2.2368</v>
       </c>
       <c r="N7" t="n">
         <v>194</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.6183</v>
+        <v>1.958</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5541</v>
+        <v>0.6704</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2324</v>
+        <v>0.3362</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6183</v>
+        <v>1.958</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6183</v>
+        <v>1.958</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6183</v>
+        <v>1.958</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6183</v>
+        <v>1.958</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.6183</v>
+        <v>1.958</v>
       </c>
       <c r="N8" t="n">
         <v>144</v>
@@ -814,216 +814,216 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.3419</v>
+        <v>1.6236</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4595</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1207</v>
+        <v>0.2029</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3419</v>
+        <v>1.6236</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3419</v>
+        <v>1.8506</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0.227</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3419</v>
+        <v>1.8506</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3419</v>
+        <v>1.8506</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0.227</v>
       </c>
       <c r="K9" t="n">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M9" t="n">
-        <v>1.3419</v>
+        <v>1.6236</v>
       </c>
       <c r="N9" t="n">
-        <v>144</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.3027</v>
+        <v>1.4601</v>
       </c>
       <c r="C10" t="n">
-        <v>0.446</v>
+        <v>0.4999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1049</v>
+        <v>0.1378</v>
       </c>
       <c r="E10" t="n">
-        <v>1.3027</v>
+        <v>1.4601</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5297</v>
+        <v>1.4601</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.227</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5297</v>
+        <v>1.4601</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5297</v>
+        <v>1.4601</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.227</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L10" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.3027</v>
+        <v>1.4601</v>
       </c>
       <c r="N10" t="n">
-        <v>194</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.2498</v>
+        <v>1.4015</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4279</v>
+        <v>0.4799</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0835</v>
+        <v>0.1144</v>
       </c>
       <c r="E11" t="n">
-        <v>1.2498</v>
+        <v>1.4015</v>
       </c>
       <c r="F11" t="n">
-        <v>0.711</v>
+        <v>1.4015</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5387999999999999</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.711</v>
+        <v>1.4015</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7177</v>
+        <v>1.4015</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5387999999999999</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="L11" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.2565</v>
+        <v>1.4015</v>
       </c>
       <c r="N11" t="n">
-        <v>193</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8844</v>
+        <v>1.3202</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3028</v>
+        <v>0.452</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0641</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8844</v>
+        <v>1.3202</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8844</v>
+        <v>0.7814</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8844</v>
+        <v>0.7814</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8844</v>
+        <v>0.7946</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8844</v>
+        <v>1.3334</v>
       </c>
       <c r="N12" t="n">
-        <v>123</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8624000000000001</v>
+        <v>1.0352</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2953</v>
+        <v>0.3544</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.073</v>
+        <v>-0.0315</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8624000000000001</v>
+        <v>1.0352</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8624000000000001</v>
+        <v>1.0352</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8624000000000001</v>
+        <v>1.0352</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8624000000000001</v>
+        <v>1.0352</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8624000000000001</v>
+        <v>1.0352</v>
       </c>
       <c r="N13" t="n">
         <v>123</v>
@@ -1044,185 +1044,185 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>refrezh</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8001</v>
+        <v>0.8581</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2739</v>
+        <v>0.2938</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.102</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8001</v>
+        <v>0.8581</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8001</v>
+        <v>0.8581</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8001</v>
+        <v>0.8581</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8001</v>
+        <v>0.8581</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8001</v>
+        <v>0.8581</v>
       </c>
       <c r="N14" t="n">
-        <v>123</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.537</v>
+        <v>0.8001</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1839</v>
+        <v>0.2739</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2044</v>
+        <v>-0.1252</v>
       </c>
       <c r="E15" t="n">
-        <v>0.537</v>
+        <v>0.8001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.537</v>
+        <v>0.8001</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.537</v>
+        <v>0.8001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.537</v>
+        <v>0.8001</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.537</v>
+        <v>0.8001</v>
       </c>
       <c r="N15" t="n">
-        <v>137</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>refrezh</t>
+          <t>swag</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.502</v>
+        <v>0.7359</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1719</v>
+        <v>0.252</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2186</v>
+        <v>-0.1507</v>
       </c>
       <c r="E16" t="n">
-        <v>0.502</v>
+        <v>0.7359</v>
       </c>
       <c r="F16" t="n">
-        <v>0.502</v>
+        <v>0.7359</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.502</v>
+        <v>0.7359</v>
       </c>
       <c r="I16" t="n">
-        <v>0.502</v>
+        <v>0.7359</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.502</v>
+        <v>0.7359</v>
       </c>
       <c r="N16" t="n">
-        <v>144</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>swag</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.375</v>
+        <v>0.537</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1284</v>
+        <v>0.1839</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2699</v>
+        <v>-0.23</v>
       </c>
       <c r="E17" t="n">
-        <v>0.375</v>
+        <v>0.537</v>
       </c>
       <c r="F17" t="n">
-        <v>0.375</v>
+        <v>0.537</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.375</v>
+        <v>0.537</v>
       </c>
       <c r="I17" t="n">
-        <v>0.375</v>
+        <v>0.537</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.375</v>
+        <v>0.537</v>
       </c>
       <c r="N17" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18">
@@ -1238,7 +1238,7 @@
         <v>0.0281</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3882</v>
+        <v>-0.4112</v>
       </c>
       <c r="E18" t="n">
         <v>0.0822</v>
@@ -1274,139 +1274,139 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.1218</v>
+        <v>-0.0526</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0417</v>
+        <v>-0.018</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4706</v>
+        <v>-0.4649</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1218</v>
+        <v>-0.0526</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1218</v>
+        <v>-0.315</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.2624</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1218</v>
+        <v>-0.315</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1218</v>
+        <v>-0.3203</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.2624</v>
       </c>
       <c r="K19" t="n">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1218</v>
+        <v>-0.05789999999999995</v>
       </c>
       <c r="N19" t="n">
-        <v>144</v>
+        <v>193</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1394</v>
+        <v>-0.1218</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0477</v>
+        <v>-0.0417</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4777</v>
+        <v>-0.4924</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1394</v>
+        <v>-0.1218</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1394</v>
+        <v>-0.1218</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1394</v>
+        <v>-0.1218</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1394</v>
+        <v>-0.1218</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1394</v>
+        <v>-0.1218</v>
       </c>
       <c r="N20" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.164</v>
+        <v>-0.1394</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0562</v>
+        <v>-0.0477</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4876</v>
+        <v>-0.4994</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.164</v>
+        <v>-0.1394</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4264</v>
+        <v>-0.1394</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2624</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4264</v>
+        <v>-0.1394</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4304</v>
+        <v>-0.1394</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2624</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="L21" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.168</v>
+        <v>-0.1394</v>
       </c>
       <c r="N21" t="n">
-        <v>193</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22">
@@ -1422,7 +1422,7 @@
         <v>-0.0963</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.535</v>
+        <v>-0.556</v>
       </c>
       <c r="E22" t="n">
         <v>-0.2813</v>
@@ -1468,7 +1468,7 @@
         <v>-0.1097</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5508</v>
+        <v>-0.5716</v>
       </c>
       <c r="E23" t="n">
         <v>-0.3205</v>
@@ -1514,7 +1514,7 @@
         <v>-0.1283</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5728</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="E24" t="n">
         <v>-0.3748</v>
@@ -1560,7 +1560,7 @@
         <v>-0.1938</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.65</v>
+        <v>-0.6694</v>
       </c>
       <c r="E25" t="n">
         <v>-0.5659</v>
@@ -1606,7 +1606,7 @@
         <v>-0.3837</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.8741</v>
+        <v>-0.8904</v>
       </c>
       <c r="E26" t="n">
         <v>-1.1208</v>
@@ -1652,7 +1652,7 @@
         <v>-0.4554</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.9587</v>
+        <v>-0.9739</v>
       </c>
       <c r="E27" t="n">
         <v>-1.3302</v>
@@ -1698,7 +1698,7 @@
         <v>-0.5835</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.1098</v>
+        <v>-1.1229</v>
       </c>
       <c r="E28" t="n">
         <v>-1.7042</v>
@@ -1744,7 +1744,7 @@
         <v>-0.6193</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.152</v>
+        <v>-1.1645</v>
       </c>
       <c r="E29" t="n">
         <v>-1.8087</v>
@@ -1790,7 +1790,7 @@
         <v>-1.3456</v>
       </c>
       <c r="D30" t="n">
-        <v>-2.009</v>
+        <v>-2.0097</v>
       </c>
       <c r="E30" t="n">
         <v>-3.9301</v>
@@ -1836,7 +1836,7 @@
         <v>-1.4101</v>
       </c>
       <c r="D31" t="n">
-        <v>-2.0851</v>
+        <v>-2.0846</v>
       </c>
       <c r="E31" t="n">
         <v>-4.1183</v>

--- a/database/event/4205/event_4205_evp_summary.xlsx
+++ b/database/event/4205/event_4205_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.2347</v>
+        <v>5.8517</v>
       </c>
       <c r="C2" t="n">
-        <v>2.4771</v>
+        <v>2.0036</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4384</v>
+        <v>2.0037</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2347</v>
+        <v>5.8517</v>
       </c>
       <c r="F2" t="n">
-        <v>5.0829</v>
+        <v>3.7768</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1518</v>
+        <v>2.0749</v>
       </c>
       <c r="H2" t="n">
-        <v>5.6669</v>
+        <v>4.9333</v>
       </c>
       <c r="I2" t="n">
-        <v>5.7627</v>
+        <v>5.3474</v>
       </c>
       <c r="J2" t="n">
-        <v>2.1518</v>
+        <v>2.0749</v>
       </c>
       <c r="K2" t="n">
         <v>125</v>
@@ -529,7 +529,7 @@
         <v>68</v>
       </c>
       <c r="M2" t="n">
-        <v>7.9145</v>
+        <v>7.4223</v>
       </c>
       <c r="N2" t="n">
         <v>193</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.8081</v>
+        <v>5.4241</v>
       </c>
       <c r="C3" t="n">
-        <v>2.331</v>
+        <v>1.8571</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2684</v>
+        <v>1.8107</v>
       </c>
       <c r="E3" t="n">
-        <v>6.8081</v>
+        <v>5.4241</v>
       </c>
       <c r="F3" t="n">
-        <v>4.7451</v>
+        <v>3.6192</v>
       </c>
       <c r="G3" t="n">
-        <v>2.063</v>
+        <v>1.8049</v>
       </c>
       <c r="H3" t="n">
-        <v>5.1373</v>
+        <v>4.5873</v>
       </c>
       <c r="I3" t="n">
-        <v>5.2241</v>
+        <v>4.9724</v>
       </c>
       <c r="J3" t="n">
-        <v>2.063</v>
+        <v>1.8049</v>
       </c>
       <c r="K3" t="n">
         <v>125</v>
@@ -575,7 +575,7 @@
         <v>68</v>
       </c>
       <c r="M3" t="n">
-        <v>7.287100000000001</v>
+        <v>6.7773</v>
       </c>
       <c r="N3" t="n">
         <v>193</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.1714</v>
+        <v>3.7003</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4282</v>
+        <v>1.2669</v>
       </c>
       <c r="D4" t="n">
-        <v>1.218</v>
+        <v>1.0325</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1714</v>
+        <v>3.7003</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3333</v>
+        <v>2.9109</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8381</v>
+        <v>0.7894</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3333</v>
+        <v>3.032</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3333</v>
+        <v>3.032</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8381</v>
+        <v>0.7894</v>
       </c>
       <c r="K4" t="n">
         <v>126</v>
@@ -621,7 +621,7 @@
         <v>68</v>
       </c>
       <c r="M4" t="n">
-        <v>4.1714</v>
+        <v>3.8214</v>
       </c>
       <c r="N4" t="n">
         <v>194</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.4502</v>
+        <v>3.1315</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1813</v>
+        <v>1.0722</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9306</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4502</v>
+        <v>3.1315</v>
       </c>
       <c r="F5" t="n">
-        <v>3.4502</v>
+        <v>3.1315</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3.4502</v>
+        <v>3.5164</v>
       </c>
       <c r="I5" t="n">
-        <v>3.4502</v>
+        <v>3.5164</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4502</v>
+        <v>3.5164</v>
       </c>
       <c r="N5" t="n">
         <v>123</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.6458</v>
+        <v>2.9797</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9059</v>
+        <v>1.0202</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6102</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6458</v>
+        <v>2.9797</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5635</v>
+        <v>1.6164</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0823</v>
+        <v>1.3633</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5635</v>
+        <v>1.6164</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5899</v>
+        <v>1.7521</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0823</v>
+        <v>1.3633</v>
       </c>
       <c r="K6" t="n">
         <v>125</v>
@@ -713,7 +713,7 @@
         <v>68</v>
       </c>
       <c r="M6" t="n">
-        <v>2.6722</v>
+        <v>3.1154</v>
       </c>
       <c r="N6" t="n">
         <v>193</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.2368</v>
+        <v>2.657</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7659</v>
+        <v>0.9097</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4472</v>
+        <v>0.5615</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2368</v>
+        <v>2.657</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3967</v>
+        <v>2.3566</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1599</v>
+        <v>0.3004</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3967</v>
+        <v>2.3566</v>
       </c>
       <c r="I7" t="n">
-        <v>2.3967</v>
+        <v>2.3566</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1599</v>
+        <v>0.3004</v>
       </c>
       <c r="K7" t="n">
         <v>126</v>
@@ -759,7 +759,7 @@
         <v>68</v>
       </c>
       <c r="M7" t="n">
-        <v>2.2368</v>
+        <v>2.657</v>
       </c>
       <c r="N7" t="n">
         <v>194</v>
@@ -768,231 +768,231 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.958</v>
+        <v>2.1265</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6704</v>
+        <v>0.7281</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3362</v>
+        <v>0.322</v>
       </c>
       <c r="E8" t="n">
-        <v>1.958</v>
+        <v>2.1265</v>
       </c>
       <c r="F8" t="n">
-        <v>1.958</v>
+        <v>2.1798</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0.0533</v>
       </c>
       <c r="H8" t="n">
-        <v>1.958</v>
+        <v>2.1798</v>
       </c>
       <c r="I8" t="n">
-        <v>1.958</v>
+        <v>2.1798</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0.0533</v>
       </c>
       <c r="K8" t="n">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M8" t="n">
-        <v>1.958</v>
+        <v>2.1265</v>
       </c>
       <c r="N8" t="n">
-        <v>144</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.6236</v>
+        <v>1.9113</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.6544</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2029</v>
+        <v>0.2248</v>
       </c>
       <c r="E9" t="n">
-        <v>1.6236</v>
+        <v>1.9113</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8506</v>
+        <v>1.9113</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.227</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8506</v>
+        <v>1.9113</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8506</v>
+        <v>1.9113</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.227</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="L9" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.6236</v>
+        <v>1.9113</v>
       </c>
       <c r="N9" t="n">
-        <v>194</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.4601</v>
+        <v>1.8772</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4999</v>
+        <v>0.6427</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1378</v>
+        <v>0.2094</v>
       </c>
       <c r="E10" t="n">
-        <v>1.4601</v>
+        <v>1.8772</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4601</v>
+        <v>0.9444</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.9328</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4601</v>
+        <v>0.9444</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4601</v>
+        <v>1.0237</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.9328</v>
       </c>
       <c r="K10" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M10" t="n">
-        <v>1.4601</v>
+        <v>1.9565</v>
       </c>
       <c r="N10" t="n">
-        <v>123</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.4015</v>
+        <v>1.5501</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4799</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1144</v>
+        <v>0.0618</v>
       </c>
       <c r="E11" t="n">
-        <v>1.4015</v>
+        <v>1.5501</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4015</v>
+        <v>1.5501</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.4015</v>
+        <v>1.5501</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4015</v>
+        <v>1.5501</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.4015</v>
+        <v>1.5501</v>
       </c>
       <c r="N11" t="n">
-        <v>144</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.3202</v>
+        <v>1.4447</v>
       </c>
       <c r="C12" t="n">
-        <v>0.452</v>
+        <v>0.4946</v>
       </c>
       <c r="D12" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0142</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3202</v>
+        <v>1.4447</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7814</v>
+        <v>1.4447</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5387999999999999</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7814</v>
+        <v>1.4447</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7946</v>
+        <v>1.4447</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5387999999999999</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="L12" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3334</v>
+        <v>1.4447</v>
       </c>
       <c r="N12" t="n">
-        <v>193</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13">
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.0352</v>
+        <v>1.442</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3544</v>
+        <v>0.4937</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0315</v>
+        <v>0.013</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0352</v>
+        <v>1.442</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0352</v>
+        <v>1.442</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0352</v>
+        <v>1.442</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0352</v>
+        <v>1.442</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.0352</v>
+        <v>1.442</v>
       </c>
       <c r="N13" t="n">
         <v>123</v>
@@ -1044,124 +1044,124 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>refrezh</t>
+          <t>swag</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8581</v>
+        <v>1.2653</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2938</v>
+        <v>0.4332</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.102</v>
+        <v>-0.0668</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8581</v>
+        <v>1.2653</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8581</v>
+        <v>1.2653</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8581</v>
+        <v>1.2653</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8581</v>
+        <v>1.2653</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8581</v>
+        <v>1.2653</v>
       </c>
       <c r="N14" t="n">
-        <v>144</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>refrezh</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8001</v>
+        <v>0.9897</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2739</v>
+        <v>0.3389</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1252</v>
+        <v>-0.1912</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8001</v>
+        <v>0.9897</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8001</v>
+        <v>0.9897</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8001</v>
+        <v>0.9897</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8001</v>
+        <v>0.9897</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8001</v>
+        <v>0.9897</v>
       </c>
       <c r="N15" t="n">
-        <v>123</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>swag</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7359</v>
+        <v>0.9595</v>
       </c>
       <c r="C16" t="n">
-        <v>0.252</v>
+        <v>0.3285</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1507</v>
+        <v>-0.2048</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7359</v>
+        <v>0.9595</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7359</v>
+        <v>0.9595</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7359</v>
+        <v>0.9595</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7359</v>
+        <v>0.9595</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7359</v>
+        <v>0.9595</v>
       </c>
       <c r="N16" t="n">
         <v>123</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.537</v>
+        <v>0.659</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1839</v>
+        <v>0.2256</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.23</v>
+        <v>-0.3405</v>
       </c>
       <c r="E17" t="n">
-        <v>0.537</v>
+        <v>0.659</v>
       </c>
       <c r="F17" t="n">
-        <v>0.537</v>
+        <v>0.659</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.537</v>
+        <v>0.659</v>
       </c>
       <c r="I17" t="n">
-        <v>0.537</v>
+        <v>0.659</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.537</v>
+        <v>0.659</v>
       </c>
       <c r="N17" t="n">
         <v>137</v>
@@ -1228,216 +1228,216 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.0822</v>
+        <v>0.55</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0281</v>
+        <v>0.1883</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4112</v>
+        <v>-0.3897</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0822</v>
+        <v>0.55</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0822</v>
+        <v>-0.0634</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0822</v>
+        <v>-0.0634</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0822</v>
+        <v>-0.0687</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0822</v>
+        <v>0.5447</v>
       </c>
       <c r="N18" t="n">
-        <v>137</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.0526</v>
+        <v>0.3549</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.018</v>
+        <v>0.1215</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4649</v>
+        <v>-0.4778</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0526</v>
+        <v>0.3549</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.315</v>
+        <v>0.3549</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2624</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.315</v>
+        <v>0.3549</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3203</v>
+        <v>0.3549</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2624</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="L19" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.05789999999999995</v>
+        <v>0.3549</v>
       </c>
       <c r="N19" t="n">
-        <v>193</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1218</v>
+        <v>0.1856</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0417</v>
+        <v>0.0635</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4924</v>
+        <v>-0.5542</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1218</v>
+        <v>0.1856</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1218</v>
+        <v>0.1856</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1218</v>
+        <v>0.1856</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1218</v>
+        <v>0.1856</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1218</v>
+        <v>0.1856</v>
       </c>
       <c r="N20" t="n">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.1394</v>
+        <v>0.178</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0477</v>
+        <v>0.0609</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4994</v>
+        <v>-0.5577</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1394</v>
+        <v>0.178</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1394</v>
+        <v>0.178</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1394</v>
+        <v>0.178</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1394</v>
+        <v>0.178</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1394</v>
+        <v>0.178</v>
       </c>
       <c r="N21" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.2813</v>
+        <v>0.1137</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0963</v>
+        <v>0.0389</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.556</v>
+        <v>-0.5867</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2813</v>
+        <v>0.1137</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2813</v>
+        <v>0.1137</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2813</v>
+        <v>0.1137</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2813</v>
+        <v>0.1137</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2813</v>
+        <v>0.1137</v>
       </c>
       <c r="N22" t="n">
         <v>137</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.3205</v>
+        <v>0.0428</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.1097</v>
+        <v>0.0147</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5716</v>
+        <v>-0.6187</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3205</v>
+        <v>0.0428</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3205</v>
+        <v>0.0428</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3205</v>
+        <v>0.0428</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3205</v>
+        <v>0.0428</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3205</v>
+        <v>0.0428</v>
       </c>
       <c r="N23" t="n">
         <v>137</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.3748</v>
+        <v>0.0215</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1283</v>
+        <v>0.0074</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.6283</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3748</v>
+        <v>0.0215</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3748</v>
+        <v>0.0215</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3748</v>
+        <v>0.0215</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3748</v>
+        <v>0.0215</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3748</v>
+        <v>0.0215</v>
       </c>
       <c r="N24" t="n">
         <v>137</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5659</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1938</v>
+        <v>-0.0245</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6694</v>
+        <v>-0.6703</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.5659</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5659</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.5659</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5659</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.5659</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="N25" t="n">
         <v>137</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-1.1208</v>
+        <v>-0.6482</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.3837</v>
+        <v>-0.2219</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.8904</v>
+        <v>-0.9306</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.1208</v>
+        <v>-0.6482</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.1208</v>
+        <v>-0.6482</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.1208</v>
+        <v>-0.6482</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.1208</v>
+        <v>-0.6482</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.1208</v>
+        <v>-0.6482</v>
       </c>
       <c r="N26" t="n">
         <v>137</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.3302</v>
+        <v>-0.8095</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.4554</v>
+        <v>-0.2772</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.9739</v>
+        <v>-1.0035</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.3302</v>
+        <v>-0.8095</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.3302</v>
+        <v>-0.8095</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.3302</v>
+        <v>-0.8095</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.3302</v>
+        <v>-0.8095</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.3302</v>
+        <v>-0.8095</v>
       </c>
       <c r="N27" t="n">
         <v>137</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.7042</v>
+        <v>-1.0577</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.5835</v>
+        <v>-0.3621</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.1229</v>
+        <v>-1.1155</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.7042</v>
+        <v>-1.0577</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.7042</v>
+        <v>-1.0577</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.7042</v>
+        <v>-1.0577</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.7042</v>
+        <v>-1.0577</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.7042</v>
+        <v>-1.0577</v>
       </c>
       <c r="N28" t="n">
         <v>137</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.8087</v>
+        <v>-1.4621</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.6193</v>
+        <v>-0.5006</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.1645</v>
+        <v>-1.2981</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.8087</v>
+        <v>-1.4621</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.8087</v>
+        <v>-1.4621</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.8087</v>
+        <v>-1.4621</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.8087</v>
+        <v>-1.4621</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.8087</v>
+        <v>-1.4621</v>
       </c>
       <c r="N29" t="n">
         <v>144</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-3.9301</v>
+        <v>-2.9311</v>
       </c>
       <c r="C30" t="n">
-        <v>-1.3456</v>
+        <v>-1.0036</v>
       </c>
       <c r="D30" t="n">
-        <v>-2.0097</v>
+        <v>-1.9613</v>
       </c>
       <c r="E30" t="n">
-        <v>-3.9301</v>
+        <v>-2.9311</v>
       </c>
       <c r="F30" t="n">
-        <v>-3.3463</v>
+        <v>-2.6609</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.5838</v>
+        <v>-0.2702</v>
       </c>
       <c r="H30" t="n">
-        <v>-3.3463</v>
+        <v>-2.6609</v>
       </c>
       <c r="I30" t="n">
-        <v>-3.3463</v>
+        <v>-2.6609</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.5838</v>
+        <v>-0.2702</v>
       </c>
       <c r="K30" t="n">
         <v>126</v>
@@ -1817,7 +1817,7 @@
         <v>68</v>
       </c>
       <c r="M30" t="n">
-        <v>-3.9301</v>
+        <v>-2.9311</v>
       </c>
       <c r="N30" t="n">
         <v>194</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-4.1183</v>
+        <v>-3.6216</v>
       </c>
       <c r="C31" t="n">
-        <v>-1.4101</v>
+        <v>-1.24</v>
       </c>
       <c r="D31" t="n">
-        <v>-2.0846</v>
+        <v>-2.273</v>
       </c>
       <c r="E31" t="n">
-        <v>-4.1183</v>
+        <v>-3.6216</v>
       </c>
       <c r="F31" t="n">
-        <v>-3.1183</v>
+        <v>-2.6216</v>
       </c>
       <c r="G31" t="n">
         <v>-1</v>
       </c>
       <c r="H31" t="n">
-        <v>-3.1183</v>
+        <v>-2.6216</v>
       </c>
       <c r="I31" t="n">
-        <v>-3.1183</v>
+        <v>-2.6216</v>
       </c>
       <c r="J31" t="n">
         <v>-1</v>
@@ -1863,7 +1863,7 @@
         <v>68</v>
       </c>
       <c r="M31" t="n">
-        <v>-4.1183</v>
+        <v>-3.6216</v>
       </c>
       <c r="N31" t="n">
         <v>194</v>
@@ -1969,10 +1969,10 @@
         <v>1.32</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6206</v>
+        <v>0.5809</v>
       </c>
       <c r="J2" t="n">
-        <v>14.2738</v>
+        <v>13.3607</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>0.89</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1398</v>
+        <v>-0.123</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.2154</v>
+        <v>-2.829</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>0.71</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4558</v>
+        <v>-0.3013</v>
       </c>
       <c r="J4" t="n">
-        <v>-10.4834</v>
+        <v>-6.9299</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6599</v>
+        <v>-0.4422</v>
       </c>
       <c r="J5" t="n">
-        <v>-15.1777</v>
+        <v>-10.1706</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.53</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6978</v>
+        <v>-0.47</v>
       </c>
       <c r="J6" t="n">
-        <v>-16.0494</v>
+        <v>-10.81</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.61</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8031</v>
+        <v>0.7245</v>
       </c>
       <c r="J7" t="n">
-        <v>18.4713</v>
+        <v>16.6635</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>1.48</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6561</v>
+        <v>0.5868</v>
       </c>
       <c r="J8" t="n">
-        <v>15.0903</v>
+        <v>13.4964</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>1.41</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5715</v>
+        <v>0.5111</v>
       </c>
       <c r="J9" t="n">
-        <v>13.1445</v>
+        <v>11.7553</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.0264</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.9895</v>
+        <v>-0.6072</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.91</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2707</v>
+        <v>-0.1516</v>
       </c>
       <c r="J11" t="n">
-        <v>-6.2261</v>
+        <v>-3.4868</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>1.37</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9601</v>
+        <v>0.9552</v>
       </c>
       <c r="J12" t="n">
-        <v>24.0025</v>
+        <v>23.88</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.29</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7788</v>
+        <v>0.7755</v>
       </c>
       <c r="J13" t="n">
-        <v>19.47</v>
+        <v>19.3875</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>1.21</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.5866</v>
       </c>
       <c r="J14" t="n">
-        <v>14.4275</v>
+        <v>14.665</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>1.13</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3325</v>
+        <v>0.3886</v>
       </c>
       <c r="J15" t="n">
-        <v>8.3125</v>
+        <v>9.715</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.91</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4427</v>
+        <v>-0.3697</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.0675</v>
+        <v>-9.2425</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.4</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6905</v>
+        <v>0.8538</v>
       </c>
       <c r="J17" t="n">
-        <v>17.2625</v>
+        <v>21.345</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>1.09</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2584</v>
+        <v>0.2651</v>
       </c>
       <c r="J18" t="n">
-        <v>6.46</v>
+        <v>6.6275</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>0.72</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4654</v>
+        <v>-0.3019</v>
       </c>
       <c r="J19" t="n">
-        <v>-11.635</v>
+        <v>-7.5475</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5068</v>
+        <v>-0.3306</v>
       </c>
       <c r="J20" t="n">
-        <v>-12.67</v>
+        <v>-8.265000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.48</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7712</v>
+        <v>-0.5249</v>
       </c>
       <c r="J21" t="n">
-        <v>-19.28</v>
+        <v>-13.1225</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.94</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8851</v>
+        <v>1.5937</v>
       </c>
       <c r="J22" t="n">
-        <v>37.702</v>
+        <v>31.874</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.63</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3315</v>
+        <v>1.2427</v>
       </c>
       <c r="J23" t="n">
-        <v>26.63</v>
+        <v>24.854</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>1.42</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8662</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>17.324</v>
+        <v>19.728</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>1.37</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7593</v>
+        <v>0.8891</v>
       </c>
       <c r="J25" t="n">
-        <v>15.186</v>
+        <v>17.782</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>1.2</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3831</v>
+        <v>0.4968</v>
       </c>
       <c r="J26" t="n">
-        <v>7.662</v>
+        <v>9.936</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>0.75</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.2234</v>
+        <v>-0.2002</v>
       </c>
       <c r="J27" t="n">
-        <v>-4.468</v>
+        <v>-4.004</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>0.65</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3763</v>
+        <v>-0.3095</v>
       </c>
       <c r="J28" t="n">
-        <v>-7.526</v>
+        <v>-6.19</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>0.47</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.6899</v>
+        <v>-0.4794</v>
       </c>
       <c r="J29" t="n">
-        <v>-13.798</v>
+        <v>-9.587999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>0.42</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7639</v>
+        <v>-0.527</v>
       </c>
       <c r="J30" t="n">
-        <v>-15.278</v>
+        <v>-10.54</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.37</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8336</v>
+        <v>-0.5756</v>
       </c>
       <c r="J31" t="n">
-        <v>-16.672</v>
+        <v>-11.512</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.05</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1677</v>
+        <v>0.159</v>
       </c>
       <c r="J32" t="n">
-        <v>5.031</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>0.96</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.0568</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.896</v>
+        <v>-1.704</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>0.96</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.0568</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.896</v>
+        <v>-1.704</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>0.84</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3007</v>
+        <v>-0.1891</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.021000000000001</v>
+        <v>-5.673</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>0.8</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3628</v>
+        <v>-0.2296</v>
       </c>
       <c r="J36" t="n">
-        <v>-10.884</v>
+        <v>-6.888</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.4</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5896</v>
+        <v>0.7255</v>
       </c>
       <c r="J37" t="n">
-        <v>17.688</v>
+        <v>21.765</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>1.24</v>
       </c>
       <c r="I38" t="n">
-        <v>0.378</v>
+        <v>0.4651</v>
       </c>
       <c r="J38" t="n">
-        <v>11.34</v>
+        <v>13.953</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>1.18</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2795</v>
+        <v>0.3639</v>
       </c>
       <c r="J39" t="n">
-        <v>8.385</v>
+        <v>10.917</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>1.08</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1073</v>
+        <v>0.1763</v>
       </c>
       <c r="J40" t="n">
-        <v>3.219</v>
+        <v>5.289</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.0665</v>
+        <v>-0.0168</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.995</v>
+        <v>-0.504</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.26</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.7393</v>
       </c>
       <c r="J42" t="n">
-        <v>23.028</v>
+        <v>22.179</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>1.19</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5945</v>
+        <v>0.5649</v>
       </c>
       <c r="J43" t="n">
-        <v>17.835</v>
+        <v>16.947</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>1.06</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1875</v>
+        <v>0.2126</v>
       </c>
       <c r="J44" t="n">
-        <v>5.625</v>
+        <v>6.378</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>0.97</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2101</v>
+        <v>-0.15</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.303</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>0.91</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4047</v>
+        <v>-0.3419</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.141</v>
+        <v>-10.257</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>1.22</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4018</v>
+        <v>0.4657</v>
       </c>
       <c r="J47" t="n">
-        <v>12.054</v>
+        <v>13.971</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1.17</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3288</v>
+        <v>0.3744</v>
       </c>
       <c r="J48" t="n">
-        <v>9.864000000000001</v>
+        <v>11.232</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>1.02</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0435</v>
+        <v>0.0626</v>
       </c>
       <c r="J49" t="n">
-        <v>1.305</v>
+        <v>1.878</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>0.89</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2534</v>
+        <v>-0.1486</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.602</v>
+        <v>-4.458</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.85</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3167</v>
+        <v>-0.1914</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.500999999999999</v>
+        <v>-5.742</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>2.23</v>
       </c>
       <c r="I52" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J52" t="n">
-        <v>37.0674</v>
+        <v>33.0084</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.71</v>
       </c>
       <c r="I53" t="n">
-        <v>1.4415</v>
+        <v>1.322</v>
       </c>
       <c r="J53" t="n">
-        <v>25.947</v>
+        <v>23.796</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>1.49</v>
       </c>
       <c r="I54" t="n">
-        <v>0.9727</v>
+        <v>1.0729</v>
       </c>
       <c r="J54" t="n">
-        <v>17.5086</v>
+        <v>19.3122</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>1.44</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8711</v>
+        <v>1.0056</v>
       </c>
       <c r="J55" t="n">
-        <v>15.6798</v>
+        <v>18.1008</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>1.17</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2901</v>
+        <v>0.4029</v>
       </c>
       <c r="J56" t="n">
-        <v>5.2218</v>
+        <v>7.2522</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>0.87</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0441</v>
+        <v>-0.0648</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.7938</v>
+        <v>-1.1664</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>0.66</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.3724</v>
+        <v>-0.3051</v>
       </c>
       <c r="J58" t="n">
-        <v>-6.7032</v>
+        <v>-5.4918</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>0.55</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.5608</v>
+        <v>-0.4104</v>
       </c>
       <c r="J59" t="n">
-        <v>-10.0944</v>
+        <v>-7.3872</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.4</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.7989000000000001</v>
+        <v>-0.5502</v>
       </c>
       <c r="J60" t="n">
-        <v>-14.3802</v>
+        <v>-9.903600000000001</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.27</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.9683</v>
+        <v>-0.6775</v>
       </c>
       <c r="J61" t="n">
-        <v>-17.4294</v>
+        <v>-12.195</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>1.35</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5769</v>
+        <v>0.6945</v>
       </c>
       <c r="J62" t="n">
-        <v>17.307</v>
+        <v>20.835</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>1.17</v>
       </c>
       <c r="I63" t="n">
-        <v>0.3317</v>
+        <v>0.3766</v>
       </c>
       <c r="J63" t="n">
-        <v>9.951000000000001</v>
+        <v>11.298</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>1.05</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1249</v>
+        <v>0.1352</v>
       </c>
       <c r="J64" t="n">
-        <v>3.747</v>
+        <v>4.056</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>1.04</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1032</v>
+        <v>0.1123</v>
       </c>
       <c r="J65" t="n">
-        <v>3.096</v>
+        <v>3.369</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.5</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7662</v>
+        <v>-0.5213</v>
       </c>
       <c r="J66" t="n">
-        <v>-22.986</v>
+        <v>-15.639</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.44</v>
       </c>
       <c r="I67" t="n">
-        <v>1.1526</v>
+        <v>1.0904</v>
       </c>
       <c r="J67" t="n">
-        <v>34.578</v>
+        <v>32.712</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.16</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5013</v>
+        <v>0.4819</v>
       </c>
       <c r="J68" t="n">
-        <v>15.039</v>
+        <v>14.457</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>1.07</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2053</v>
+        <v>0.2387</v>
       </c>
       <c r="J69" t="n">
-        <v>6.159</v>
+        <v>7.161</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>1.01</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0188</v>
+        <v>0.0323</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.5639999999999999</v>
+        <v>0.969</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6776</v>
+        <v>-0.6232</v>
       </c>
       <c r="J71" t="n">
-        <v>-20.328</v>
+        <v>-18.696</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.14</v>
       </c>
       <c r="I72" t="n">
-        <v>0.2771</v>
+        <v>0.3145</v>
       </c>
       <c r="J72" t="n">
-        <v>8.0359</v>
+        <v>9.1205</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.1</v>
       </c>
       <c r="I73" t="n">
-        <v>0.2102</v>
+        <v>0.2366</v>
       </c>
       <c r="J73" t="n">
-        <v>6.0958</v>
+        <v>6.8614</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>1.03</v>
       </c>
       <c r="I74" t="n">
-        <v>0.06</v>
+        <v>0.0862</v>
       </c>
       <c r="J74" t="n">
-        <v>1.74</v>
+        <v>2.4998</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>0.98</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.0871</v>
+        <v>-0.04</v>
       </c>
       <c r="J75" t="n">
-        <v>-2.5259</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>0.97</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.1099</v>
+        <v>-0.0543</v>
       </c>
       <c r="J76" t="n">
-        <v>-3.1871</v>
+        <v>-1.5747</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.24</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7655</v>
+        <v>0.7239</v>
       </c>
       <c r="J77" t="n">
-        <v>22.1995</v>
+        <v>20.9931</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>1.13</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4829</v>
+        <v>0.4336</v>
       </c>
       <c r="J78" t="n">
-        <v>14.0041</v>
+        <v>12.5744</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>1.12</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4547</v>
+        <v>0.4057</v>
       </c>
       <c r="J79" t="n">
-        <v>13.1863</v>
+        <v>11.7653</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.79</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.6924</v>
+        <v>-0.6471</v>
       </c>
       <c r="J80" t="n">
-        <v>-20.0796</v>
+        <v>-18.7659</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.72</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.8595</v>
+        <v>-0.8243</v>
       </c>
       <c r="J81" t="n">
-        <v>-24.9255</v>
+        <v>-23.9047</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.72</v>
       </c>
       <c r="I82" t="n">
-        <v>1.6487</v>
+        <v>1.4231</v>
       </c>
       <c r="J82" t="n">
-        <v>37.9201</v>
+        <v>32.7313</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1.29</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7788</v>
+        <v>0.7755</v>
       </c>
       <c r="J83" t="n">
-        <v>17.9124</v>
+        <v>17.8365</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>1.24</v>
       </c>
       <c r="I84" t="n">
-        <v>0.6563</v>
+        <v>0.6581</v>
       </c>
       <c r="J84" t="n">
-        <v>15.0949</v>
+        <v>15.1363</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>0.83</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.6529</v>
+        <v>-0.5923</v>
       </c>
       <c r="J85" t="n">
-        <v>-15.0167</v>
+        <v>-13.6229</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.83</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6529</v>
+        <v>-0.5923</v>
       </c>
       <c r="J86" t="n">
-        <v>-15.0167</v>
+        <v>-13.6229</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>0.98</v>
       </c>
       <c r="I87" t="n">
-        <v>0.0165</v>
+        <v>-0.0167</v>
       </c>
       <c r="J87" t="n">
-        <v>0.3795</v>
+        <v>-0.3841</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>0.98</v>
       </c>
       <c r="I88" t="n">
-        <v>0.0165</v>
+        <v>-0.0167</v>
       </c>
       <c r="J88" t="n">
-        <v>0.3795</v>
+        <v>-0.3841</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>0.88</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1788</v>
+        <v>-0.1402</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.1124</v>
+        <v>-3.2246</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.87</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1972</v>
+        <v>-0.1508</v>
       </c>
       <c r="J90" t="n">
-        <v>-4.5356</v>
+        <v>-3.4684</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.51</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.7302999999999999</v>
+        <v>-0.4939</v>
       </c>
       <c r="J91" t="n">
-        <v>-16.7969</v>
+        <v>-11.3597</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.5</v>
       </c>
       <c r="I92" t="n">
-        <v>1.2282</v>
+        <v>1.1444</v>
       </c>
       <c r="J92" t="n">
-        <v>31.9332</v>
+        <v>29.7544</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>1.45</v>
       </c>
       <c r="I93" t="n">
-        <v>1.1266</v>
+        <v>1.0798</v>
       </c>
       <c r="J93" t="n">
-        <v>29.2916</v>
+        <v>28.0748</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>1.36</v>
       </c>
       <c r="I94" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9327</v>
       </c>
       <c r="J94" t="n">
-        <v>24.31</v>
+        <v>24.2502</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>0.85</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.6046</v>
+        <v>-0.5402</v>
       </c>
       <c r="J95" t="n">
-        <v>-15.7196</v>
+        <v>-14.0452</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.78</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.7739</v>
+        <v>-0.7235</v>
       </c>
       <c r="J96" t="n">
-        <v>-20.1214</v>
+        <v>-18.811</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.04</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1566</v>
+        <v>0.1417</v>
       </c>
       <c r="J97" t="n">
-        <v>4.0716</v>
+        <v>3.6842</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.0529</v>
+        <v>0.0208</v>
       </c>
       <c r="J98" t="n">
-        <v>1.3754</v>
+        <v>0.5407999999999999</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>0.9</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1788</v>
+        <v>-0.1243</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.6488</v>
+        <v>-3.2318</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>0.82</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3246</v>
+        <v>-0.2068</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.4396</v>
+        <v>-5.3768</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.74</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4439</v>
+        <v>-0.2858</v>
       </c>
       <c r="J101" t="n">
-        <v>-11.5414</v>
+        <v>-7.4308</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>1.53</v>
       </c>
       <c r="I102" t="n">
-        <v>1.2423</v>
+        <v>1.1609</v>
       </c>
       <c r="J102" t="n">
-        <v>33.5421</v>
+        <v>31.3443</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>1.39</v>
       </c>
       <c r="I103" t="n">
-        <v>0.9507</v>
+        <v>0.9674</v>
       </c>
       <c r="J103" t="n">
-        <v>25.6689</v>
+        <v>26.1198</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>1.31</v>
       </c>
       <c r="I104" t="n">
-        <v>0.7637</v>
+        <v>0.7972</v>
       </c>
       <c r="J104" t="n">
-        <v>20.6199</v>
+        <v>21.5244</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>1.27</v>
       </c>
       <c r="I105" t="n">
-        <v>0.6463</v>
+        <v>0.7096</v>
       </c>
       <c r="J105" t="n">
-        <v>17.4501</v>
+        <v>19.1592</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.91</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4709</v>
+        <v>-0.3939</v>
       </c>
       <c r="J106" t="n">
-        <v>-12.7143</v>
+        <v>-10.6353</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>0.9</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.1325</v>
+        <v>-0.1153</v>
       </c>
       <c r="J107" t="n">
-        <v>-3.5775</v>
+        <v>-3.1131</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>0.85</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.2219</v>
+        <v>-0.1692</v>
       </c>
       <c r="J108" t="n">
-        <v>-5.9913</v>
+        <v>-4.5684</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>0.85</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2219</v>
+        <v>-0.1692</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.9913</v>
+        <v>-4.5684</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>0.8</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.323</v>
+        <v>-0.2177</v>
       </c>
       <c r="J110" t="n">
-        <v>-8.721</v>
+        <v>-5.8779</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>0.72</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4491</v>
+        <v>-0.2948</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.1257</v>
+        <v>-7.9596</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.17</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3224</v>
+        <v>0.3697</v>
       </c>
       <c r="J112" t="n">
-        <v>9.672000000000001</v>
+        <v>11.091</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>1.12</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2428</v>
+        <v>0.2752</v>
       </c>
       <c r="J113" t="n">
-        <v>7.284</v>
+        <v>8.256</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>1.07</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1523</v>
+        <v>0.1745</v>
       </c>
       <c r="J114" t="n">
-        <v>4.569</v>
+        <v>5.235</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>0.97</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1113</v>
+        <v>-0.0547</v>
       </c>
       <c r="J115" t="n">
-        <v>-3.339</v>
+        <v>-1.641</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.91</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2249</v>
+        <v>-0.1283</v>
       </c>
       <c r="J116" t="n">
-        <v>-6.747</v>
+        <v>-3.849</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.25</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4455</v>
+        <v>0.521</v>
       </c>
       <c r="J117" t="n">
-        <v>13.365</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.07</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1639</v>
+        <v>0.1786</v>
       </c>
       <c r="J118" t="n">
-        <v>4.917</v>
+        <v>5.358</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0173</v>
+        <v>-0.0016</v>
       </c>
       <c r="J119" t="n">
-        <v>-0.519</v>
+        <v>-0.048</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>0.93</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1825</v>
+        <v>-0.1026</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.475</v>
+        <v>-3.078</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>0.87</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2841</v>
+        <v>-0.1696</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.523</v>
+        <v>-5.088</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.51</v>
       </c>
       <c r="I122" t="n">
-        <v>1.2471</v>
+        <v>1.1568</v>
       </c>
       <c r="J122" t="n">
-        <v>31.1775</v>
+        <v>28.92</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.35</v>
       </c>
       <c r="I123" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.9104</v>
       </c>
       <c r="J123" t="n">
-        <v>22.795</v>
+        <v>22.76</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>1.33</v>
       </c>
       <c r="I124" t="n">
-        <v>0.8669</v>
+        <v>0.8653</v>
       </c>
       <c r="J124" t="n">
-        <v>21.6725</v>
+        <v>21.6325</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>1.25</v>
       </c>
       <c r="I125" t="n">
-        <v>0.6764</v>
+        <v>0.6798</v>
       </c>
       <c r="J125" t="n">
-        <v>16.91</v>
+        <v>16.995</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.51</v>
       </c>
       <c r="I126" t="n">
-        <v>-1.3402</v>
+        <v>-1.3655</v>
       </c>
       <c r="J126" t="n">
-        <v>-33.505</v>
+        <v>-34.1375</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.29</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5486</v>
+        <v>0.6523</v>
       </c>
       <c r="J127" t="n">
-        <v>13.715</v>
+        <v>16.3075</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1.07</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2202</v>
+        <v>0.2178</v>
       </c>
       <c r="J128" t="n">
-        <v>5.505</v>
+        <v>5.445</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1057</v>
+        <v>-0.0892</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.6425</v>
+        <v>-2.23</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>0.68</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.5224</v>
+        <v>-0.3411</v>
       </c>
       <c r="J130" t="n">
-        <v>-13.06</v>
+        <v>-8.5275</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.45</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.8074</v>
+        <v>-0.5528</v>
       </c>
       <c r="J131" t="n">
-        <v>-20.185</v>
+        <v>-13.82</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>1.35</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5671</v>
+        <v>0.6833</v>
       </c>
       <c r="J132" t="n">
-        <v>15.8788</v>
+        <v>19.1324</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1.03</v>
       </c>
       <c r="I133" t="n">
-        <v>0.0557</v>
+        <v>0.0851</v>
       </c>
       <c r="J133" t="n">
-        <v>1.5596</v>
+        <v>2.3828</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>1</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.0296</v>
+        <v>-0.0041</v>
       </c>
       <c r="J134" t="n">
-        <v>-0.8288</v>
+        <v>-0.1148</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>0.99</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0646</v>
+        <v>-0.0251</v>
       </c>
       <c r="J135" t="n">
-        <v>-1.8088</v>
+        <v>-0.7028</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.89</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2592</v>
+        <v>-0.1511</v>
       </c>
       <c r="J136" t="n">
-        <v>-7.2576</v>
+        <v>-4.2308</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.25</v>
       </c>
       <c r="I137" t="n">
-        <v>0.7635</v>
+        <v>0.7287</v>
       </c>
       <c r="J137" t="n">
-        <v>21.378</v>
+        <v>20.4036</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>1.12</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4253</v>
+        <v>0.3908</v>
       </c>
       <c r="J138" t="n">
-        <v>11.9084</v>
+        <v>10.9424</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>1.07</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2687</v>
+        <v>0.248</v>
       </c>
       <c r="J139" t="n">
-        <v>7.5236</v>
+        <v>6.944</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>0.92</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3592</v>
+        <v>-0.3025</v>
       </c>
       <c r="J140" t="n">
-        <v>-10.0576</v>
+        <v>-8.470000000000001</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.86</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5301</v>
+        <v>-0.4741</v>
       </c>
       <c r="J141" t="n">
-        <v>-14.8428</v>
+        <v>-13.2748</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.43</v>
       </c>
       <c r="I142" t="n">
-        <v>1.0486</v>
+        <v>1.0375</v>
       </c>
       <c r="J142" t="n">
-        <v>23.0692</v>
+        <v>22.825</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>1.37</v>
       </c>
       <c r="I143" t="n">
-        <v>0.9183</v>
+        <v>0.9333</v>
       </c>
       <c r="J143" t="n">
-        <v>20.2026</v>
+        <v>20.5326</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>1.28</v>
       </c>
       <c r="I144" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="J144" t="n">
-        <v>15.4682</v>
+        <v>16.1568</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>1.21</v>
       </c>
       <c r="I145" t="n">
-        <v>0.5028</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="J145" t="n">
-        <v>11.0616</v>
+        <v>12.6302</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>1.01</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.0857</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="J146" t="n">
-        <v>-1.8854</v>
+        <v>-0.1848</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>0.87</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.1639</v>
+        <v>-0.1413</v>
       </c>
       <c r="J147" t="n">
-        <v>-3.6058</v>
+        <v>-3.1086</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>0.86</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1809</v>
+        <v>-0.1522</v>
       </c>
       <c r="J148" t="n">
-        <v>-3.9798</v>
+        <v>-3.3484</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>0.8</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2844</v>
+        <v>-0.2137</v>
       </c>
       <c r="J149" t="n">
-        <v>-6.2568</v>
+        <v>-4.7014</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>0.73</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.416</v>
+        <v>-0.2793</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.151999999999999</v>
+        <v>-6.1446</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.64</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5481</v>
+        <v>-0.3643</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.0582</v>
+        <v>-8.0146</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>1.65</v>
       </c>
       <c r="I152" t="n">
-        <v>1.4894</v>
+        <v>1.3177</v>
       </c>
       <c r="J152" t="n">
-        <v>41.7032</v>
+        <v>36.8956</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>1.48</v>
       </c>
       <c r="I153" t="n">
-        <v>1.1592</v>
+        <v>1.1055</v>
       </c>
       <c r="J153" t="n">
-        <v>32.4576</v>
+        <v>30.954</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>1.26</v>
       </c>
       <c r="I154" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.6916</v>
       </c>
       <c r="J154" t="n">
-        <v>18.5024</v>
+        <v>19.3648</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.97</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2759</v>
+        <v>-0.1934</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.7252</v>
+        <v>-5.4152</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.87</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5688</v>
+        <v>-0.4995</v>
       </c>
       <c r="J156" t="n">
-        <v>-15.9264</v>
+        <v>-13.986</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>0.95</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.0293</v>
+        <v>-0.0505</v>
       </c>
       <c r="J157" t="n">
-        <v>-0.8204</v>
+        <v>-1.414</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>0.91</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.1043</v>
+        <v>-0.1</v>
       </c>
       <c r="J158" t="n">
-        <v>-2.9204</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>0.8</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.3063</v>
+        <v>-0.2157</v>
       </c>
       <c r="J159" t="n">
-        <v>-8.5764</v>
+        <v>-6.0396</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>0.8</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3063</v>
+        <v>-0.2157</v>
       </c>
       <c r="J160" t="n">
-        <v>-8.5764</v>
+        <v>-6.0396</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>0.55</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.6726</v>
+        <v>-0.4515</v>
       </c>
       <c r="J161" t="n">
-        <v>-18.8328</v>
+        <v>-12.642</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.19</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3719</v>
+        <v>0.4228</v>
       </c>
       <c r="J162" t="n">
-        <v>11.157</v>
+        <v>12.684</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>1.17</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3424</v>
+        <v>0.3854</v>
       </c>
       <c r="J163" t="n">
-        <v>10.272</v>
+        <v>11.562</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>1</v>
       </c>
       <c r="I164" t="n">
-        <v>0.008</v>
+        <v>0.0008</v>
       </c>
       <c r="J164" t="n">
-        <v>0.24</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>0.89</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2423</v>
+        <v>-0.1444</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.269</v>
+        <v>-4.332</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>0.71</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5057</v>
+        <v>-0.3258</v>
       </c>
       <c r="J166" t="n">
-        <v>-15.171</v>
+        <v>-9.773999999999999</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1.45</v>
       </c>
       <c r="I167" t="n">
-        <v>1.1721</v>
+        <v>1.1032</v>
       </c>
       <c r="J167" t="n">
-        <v>35.163</v>
+        <v>33.096</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>1.19</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5806</v>
+        <v>0.5579</v>
       </c>
       <c r="J168" t="n">
-        <v>17.418</v>
+        <v>16.737</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>1.09</v>
       </c>
       <c r="I169" t="n">
-        <v>0.272</v>
+        <v>0.2958</v>
       </c>
       <c r="J169" t="n">
-        <v>8.16</v>
+        <v>8.874000000000001</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>0.96</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2566</v>
+        <v>-0.1909</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.698</v>
+        <v>-5.727</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6782</v>
+        <v>-0.6237</v>
       </c>
       <c r="J171" t="n">
-        <v>-20.346</v>
+        <v>-18.711</v>
       </c>
     </row>
     <row r="172">
@@ -8769,10 +8769,10 @@
         <v>2.02</v>
       </c>
       <c r="I172" t="n">
-        <v>1.9757</v>
+        <v>1.6794</v>
       </c>
       <c r="J172" t="n">
-        <v>39.514</v>
+        <v>33.588</v>
       </c>
     </row>
     <row r="173">
@@ -8809,10 +8809,10 @@
         <v>1.89</v>
       </c>
       <c r="I173" t="n">
-        <v>1.7981</v>
+        <v>1.5354</v>
       </c>
       <c r="J173" t="n">
-        <v>35.962</v>
+        <v>30.708</v>
       </c>
     </row>
     <row r="174">
@@ -8849,10 +8849,10 @@
         <v>1.41</v>
       </c>
       <c r="I174" t="n">
-        <v>0.839</v>
+        <v>0.9669</v>
       </c>
       <c r="J174" t="n">
-        <v>16.78</v>
+        <v>19.338</v>
       </c>
     </row>
     <row r="175">
@@ -8889,10 +8889,10 @@
         <v>1.25</v>
       </c>
       <c r="I175" t="n">
-        <v>0.4934</v>
+        <v>0.615</v>
       </c>
       <c r="J175" t="n">
-        <v>9.868</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="176">
@@ -8929,10 +8929,10 @@
         <v>1.06</v>
       </c>
       <c r="I176" t="n">
-        <v>0.0204</v>
+        <v>0.1123</v>
       </c>
       <c r="J176" t="n">
-        <v>0.408</v>
+        <v>2.246</v>
       </c>
     </row>
     <row r="177">
@@ -8969,10 +8969,10 @@
         <v>0.96</v>
       </c>
       <c r="I177" t="n">
-        <v>0.1322</v>
+        <v>0.1346</v>
       </c>
       <c r="J177" t="n">
-        <v>2.644</v>
+        <v>2.692</v>
       </c>
     </row>
     <row r="178">
@@ -9009,10 +9009,10 @@
         <v>0.49</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.6569</v>
+        <v>-0.4603</v>
       </c>
       <c r="J178" t="n">
-        <v>-13.138</v>
+        <v>-9.206</v>
       </c>
     </row>
     <row r="179">
@@ -9049,10 +9049,10 @@
         <v>0.46</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.7040999999999999</v>
+        <v>-0.4884</v>
       </c>
       <c r="J179" t="n">
-        <v>-14.082</v>
+        <v>-9.768000000000001</v>
       </c>
     </row>
     <row r="180">
@@ -9089,10 +9089,10 @@
         <v>0.37</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.8329</v>
+        <v>-0.5752</v>
       </c>
       <c r="J180" t="n">
-        <v>-16.658</v>
+        <v>-11.504</v>
       </c>
     </row>
     <row r="181">
@@ -9129,10 +9129,10 @@
         <v>0.37</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.8329</v>
+        <v>-0.5752</v>
       </c>
       <c r="J181" t="n">
-        <v>-16.658</v>
+        <v>-11.504</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4205/event_4205_evp_summary.xlsx
+++ b/database/event/4205/event_4205_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.8517</v>
+        <v>5.5645</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0036</v>
+        <v>1.9052</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0037</v>
+        <v>1.9089</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8517</v>
+        <v>5.5645</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7768</v>
+        <v>3.5077</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0749</v>
+        <v>2.0568</v>
       </c>
       <c r="H2" t="n">
-        <v>4.9333</v>
+        <v>4.9523</v>
       </c>
       <c r="I2" t="n">
-        <v>5.3474</v>
+        <v>5.2108</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0749</v>
+        <v>2.0568</v>
       </c>
       <c r="K2" t="n">
         <v>125</v>
@@ -529,7 +529,7 @@
         <v>68</v>
       </c>
       <c r="M2" t="n">
-        <v>7.4223</v>
+        <v>7.2676</v>
       </c>
       <c r="N2" t="n">
         <v>193</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.4241</v>
+        <v>5.3117</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8571</v>
+        <v>1.8187</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8107</v>
+        <v>1.7938</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4241</v>
+        <v>5.3117</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6192</v>
+        <v>3.3708</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8049</v>
+        <v>1.9409</v>
       </c>
       <c r="H3" t="n">
-        <v>4.5873</v>
+        <v>4.6526</v>
       </c>
       <c r="I3" t="n">
-        <v>4.9724</v>
+        <v>4.8955</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8049</v>
+        <v>1.9409</v>
       </c>
       <c r="K3" t="n">
         <v>125</v>
@@ -575,7 +575,7 @@
         <v>68</v>
       </c>
       <c r="M3" t="n">
-        <v>6.7773</v>
+        <v>6.8364</v>
       </c>
       <c r="N3" t="n">
         <v>193</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.7003</v>
+        <v>3.3095</v>
       </c>
       <c r="C4" t="n">
-        <v>1.2669</v>
+        <v>1.1331</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0325</v>
+        <v>0.8823</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7003</v>
+        <v>3.3095</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9109</v>
+        <v>2.5589</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7894</v>
+        <v>0.7506</v>
       </c>
       <c r="H4" t="n">
-        <v>3.032</v>
+        <v>2.8758</v>
       </c>
       <c r="I4" t="n">
-        <v>3.032</v>
+        <v>2.8758</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7894</v>
+        <v>0.7506</v>
       </c>
       <c r="K4" t="n">
         <v>126</v>
@@ -621,7 +621,7 @@
         <v>68</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8214</v>
+        <v>3.6264</v>
       </c>
       <c r="N4" t="n">
         <v>194</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.1315</v>
+        <v>2.9047</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0722</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1315</v>
+        <v>2.9047</v>
       </c>
       <c r="F5" t="n">
-        <v>3.1315</v>
+        <v>2.9047</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5164</v>
+        <v>3.6326</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5164</v>
+        <v>3.6326</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5164</v>
+        <v>3.6326</v>
       </c>
       <c r="N5" t="n">
         <v>123</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.9797</v>
+        <v>2.8893</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0202</v>
+        <v>0.9893</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7072000000000001</v>
+        <v>0.6911</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9797</v>
+        <v>2.8893</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6164</v>
+        <v>1.6234</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3633</v>
+        <v>1.2659</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6164</v>
+        <v>1.6234</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7521</v>
+        <v>1.7081</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3633</v>
+        <v>1.2659</v>
       </c>
       <c r="K6" t="n">
         <v>125</v>
@@ -713,7 +713,7 @@
         <v>68</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1154</v>
+        <v>2.974</v>
       </c>
       <c r="N6" t="n">
         <v>193</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.657</v>
+        <v>2.4623</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9097</v>
+        <v>0.8431</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5615</v>
+        <v>0.4967</v>
       </c>
       <c r="E7" t="n">
-        <v>2.657</v>
+        <v>2.4623</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3566</v>
+        <v>2.2224</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3004</v>
+        <v>0.2399</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3566</v>
+        <v>2.2224</v>
       </c>
       <c r="I7" t="n">
-        <v>2.3566</v>
+        <v>2.2224</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3004</v>
+        <v>0.2399</v>
       </c>
       <c r="K7" t="n">
         <v>126</v>
@@ -759,7 +759,7 @@
         <v>68</v>
       </c>
       <c r="M7" t="n">
-        <v>2.657</v>
+        <v>2.4623</v>
       </c>
       <c r="N7" t="n">
         <v>194</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.1265</v>
+        <v>1.9754</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7281</v>
+        <v>0.6764</v>
       </c>
       <c r="D8" t="n">
-        <v>0.322</v>
+        <v>0.275</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1265</v>
+        <v>1.9754</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1798</v>
+        <v>2.0629</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0533</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>2.1798</v>
+        <v>2.0629</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1798</v>
+        <v>2.0629</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0533</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="K8" t="n">
         <v>126</v>
@@ -805,7 +805,7 @@
         <v>68</v>
       </c>
       <c r="M8" t="n">
-        <v>2.1265</v>
+        <v>1.9754</v>
       </c>
       <c r="N8" t="n">
         <v>194</v>
@@ -814,93 +814,93 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.9113</v>
+        <v>1.8469</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6544</v>
+        <v>0.6324</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2248</v>
+        <v>0.2165</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9113</v>
+        <v>1.8469</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9113</v>
+        <v>0.9705</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.8764</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9113</v>
+        <v>0.9705</v>
       </c>
       <c r="I9" t="n">
-        <v>1.9113</v>
+        <v>1.0212</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.8764</v>
       </c>
       <c r="K9" t="n">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M9" t="n">
-        <v>1.9113</v>
+        <v>1.8976</v>
       </c>
       <c r="N9" t="n">
-        <v>144</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.8772</v>
+        <v>1.8188</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6427</v>
+        <v>0.6227</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2094</v>
+        <v>0.2038</v>
       </c>
       <c r="E10" t="n">
-        <v>1.8772</v>
+        <v>1.8188</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9444</v>
+        <v>1.8188</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9328</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9444</v>
+        <v>1.8188</v>
       </c>
       <c r="I10" t="n">
-        <v>1.0237</v>
+        <v>1.8188</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9328</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="L10" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.9565</v>
+        <v>1.8188</v>
       </c>
       <c r="N10" t="n">
-        <v>193</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.5501</v>
+        <v>1.5355</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0618</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>1.5501</v>
+        <v>1.5355</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5501</v>
+        <v>1.5355</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5501</v>
+        <v>1.5355</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5501</v>
+        <v>1.5355</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.5501</v>
+        <v>1.5355</v>
       </c>
       <c r="N11" t="n">
         <v>123</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.4447</v>
+        <v>1.3864</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4946</v>
+        <v>0.4747</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0142</v>
+        <v>0.0069</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4447</v>
+        <v>1.3864</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4447</v>
+        <v>1.3864</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4447</v>
+        <v>1.3864</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4447</v>
+        <v>1.3864</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.4447</v>
+        <v>1.3864</v>
       </c>
       <c r="N12" t="n">
         <v>144</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.442</v>
+        <v>1.3493</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4937</v>
+        <v>0.462</v>
       </c>
       <c r="D13" t="n">
-        <v>0.013</v>
+        <v>-0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>1.442</v>
+        <v>1.3493</v>
       </c>
       <c r="F13" t="n">
-        <v>1.442</v>
+        <v>1.3493</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.442</v>
+        <v>1.3493</v>
       </c>
       <c r="I13" t="n">
-        <v>1.442</v>
+        <v>1.3493</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.442</v>
+        <v>1.3493</v>
       </c>
       <c r="N13" t="n">
         <v>123</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.2653</v>
+        <v>1.1476</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4332</v>
+        <v>0.3929</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0668</v>
+        <v>-0.1018</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2653</v>
+        <v>1.1476</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2653</v>
+        <v>1.1476</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2653</v>
+        <v>1.1476</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2653</v>
+        <v>1.1476</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2653</v>
+        <v>1.1476</v>
       </c>
       <c r="N14" t="n">
         <v>123</v>
@@ -1090,185 +1090,185 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>refrezh</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9897</v>
+        <v>0.952</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3389</v>
+        <v>0.326</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1912</v>
+        <v>-0.1908</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9897</v>
+        <v>0.952</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9897</v>
+        <v>0.952</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9897</v>
+        <v>0.952</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9897</v>
+        <v>0.952</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9897</v>
+        <v>0.952</v>
       </c>
       <c r="N15" t="n">
-        <v>144</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>refrezh</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9595</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3285</v>
+        <v>0.3236</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2048</v>
+        <v>-0.194</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9595</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9595</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9595</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9595</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9595</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>123</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.659</v>
+        <v>0.6328</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2256</v>
+        <v>0.2167</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3405</v>
+        <v>-0.3361</v>
       </c>
       <c r="E17" t="n">
-        <v>0.659</v>
+        <v>0.6328</v>
       </c>
       <c r="F17" t="n">
-        <v>0.659</v>
+        <v>0.0427</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.5901</v>
       </c>
       <c r="H17" t="n">
-        <v>0.659</v>
+        <v>0.0427</v>
       </c>
       <c r="I17" t="n">
-        <v>0.659</v>
+        <v>0.0449</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.5901</v>
       </c>
       <c r="K17" t="n">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M17" t="n">
-        <v>0.659</v>
+        <v>0.635</v>
       </c>
       <c r="N17" t="n">
-        <v>137</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.55</v>
+        <v>0.5816</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1883</v>
+        <v>0.1991</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3897</v>
+        <v>-0.3594</v>
       </c>
       <c r="E18" t="n">
-        <v>0.55</v>
+        <v>0.5816</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0634</v>
+        <v>0.5816</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6133999999999999</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0634</v>
+        <v>0.5816</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0687</v>
+        <v>0.5816</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6133999999999999</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="L18" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5447</v>
+        <v>0.5816</v>
       </c>
       <c r="N18" t="n">
-        <v>193</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.3549</v>
+        <v>0.2896</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1215</v>
+        <v>0.0992</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4778</v>
+        <v>-0.4924</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3549</v>
+        <v>0.2896</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3549</v>
+        <v>0.2896</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3549</v>
+        <v>0.2896</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3549</v>
+        <v>0.2896</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3549</v>
+        <v>0.2896</v>
       </c>
       <c r="N19" t="n">
         <v>137</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1856</v>
+        <v>0.1832</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0635</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5542</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1856</v>
+        <v>0.1832</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1856</v>
+        <v>0.1832</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1856</v>
+        <v>0.1832</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1856</v>
+        <v>0.1832</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1856</v>
+        <v>0.1832</v>
       </c>
       <c r="N20" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.178</v>
+        <v>0.1333</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0609</v>
+        <v>0.0456</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5577</v>
+        <v>-0.5635</v>
       </c>
       <c r="E21" t="n">
-        <v>0.178</v>
+        <v>0.1333</v>
       </c>
       <c r="F21" t="n">
-        <v>0.178</v>
+        <v>0.1333</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.178</v>
+        <v>0.1333</v>
       </c>
       <c r="I21" t="n">
-        <v>0.178</v>
+        <v>0.1333</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.178</v>
+        <v>0.1333</v>
       </c>
       <c r="N21" t="n">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1137</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0389</v>
+        <v>0.0251</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5867</v>
+        <v>-0.5908</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1137</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1137</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1137</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1137</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1137</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="N22" t="n">
         <v>137</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0428</v>
+        <v>0.0461</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0147</v>
+        <v>0.0158</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6187</v>
+        <v>-0.6032</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0428</v>
+        <v>0.0461</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0428</v>
+        <v>0.0461</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0428</v>
+        <v>0.0461</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0428</v>
+        <v>0.0461</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0428</v>
+        <v>0.0461</v>
       </c>
       <c r="N23" t="n">
         <v>137</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0215</v>
+        <v>-0.0171</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0074</v>
+        <v>-0.0059</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6283</v>
+        <v>-0.632</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0215</v>
+        <v>-0.0171</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0215</v>
+        <v>-0.0171</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0215</v>
+        <v>-0.0171</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0215</v>
+        <v>-0.0171</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0215</v>
+        <v>-0.0171</v>
       </c>
       <c r="N24" t="n">
         <v>137</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.1454</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0245</v>
+        <v>-0.0498</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6703</v>
+        <v>-0.6904</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.1454</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.1454</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.1454</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.1454</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.1454</v>
       </c>
       <c r="N25" t="n">
         <v>137</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.6482</v>
+        <v>-0.6683</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.2219</v>
+        <v>-0.2288</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.9306</v>
+        <v>-0.9284</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.6482</v>
+        <v>-0.6683</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6482</v>
+        <v>-0.6683</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.6482</v>
+        <v>-0.6683</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6482</v>
+        <v>-0.6683</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.6482</v>
+        <v>-0.6683</v>
       </c>
       <c r="N26" t="n">
         <v>137</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.8095</v>
+        <v>-0.8514</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.2772</v>
+        <v>-0.2915</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.0035</v>
+        <v>-1.0118</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.8095</v>
+        <v>-0.8514</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.8095</v>
+        <v>-0.8514</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.8095</v>
+        <v>-0.8514</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.8095</v>
+        <v>-0.8514</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.8095</v>
+        <v>-0.8514</v>
       </c>
       <c r="N27" t="n">
         <v>137</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.0577</v>
+        <v>-1.1005</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.3621</v>
+        <v>-0.3768</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.1155</v>
+        <v>-1.1252</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.0577</v>
+        <v>-1.1005</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.0577</v>
+        <v>-1.1005</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.0577</v>
+        <v>-1.1005</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.0577</v>
+        <v>-1.1005</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.0577</v>
+        <v>-1.1005</v>
       </c>
       <c r="N28" t="n">
         <v>137</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.4621</v>
+        <v>-1.3843</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.5006</v>
+        <v>-0.474</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.2981</v>
+        <v>-1.2544</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.4621</v>
+        <v>-1.3843</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.4621</v>
+        <v>-1.3843</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.4621</v>
+        <v>-1.3843</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.4621</v>
+        <v>-1.3843</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.4621</v>
+        <v>-1.3843</v>
       </c>
       <c r="N29" t="n">
         <v>144</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.9311</v>
+        <v>-2.8581</v>
       </c>
       <c r="C30" t="n">
-        <v>-1.0036</v>
+        <v>-0.9786</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.9613</v>
+        <v>-1.9253</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.9311</v>
+        <v>-2.8581</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.6609</v>
+        <v>-2.5673</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.2702</v>
+        <v>-0.2908</v>
       </c>
       <c r="H30" t="n">
-        <v>-2.6609</v>
+        <v>-2.5673</v>
       </c>
       <c r="I30" t="n">
-        <v>-2.6609</v>
+        <v>-2.5673</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.2702</v>
+        <v>-0.2908</v>
       </c>
       <c r="K30" t="n">
         <v>126</v>
@@ -1817,7 +1817,7 @@
         <v>68</v>
       </c>
       <c r="M30" t="n">
-        <v>-2.9311</v>
+        <v>-2.8581</v>
       </c>
       <c r="N30" t="n">
         <v>194</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-3.6216</v>
+        <v>-3.5299</v>
       </c>
       <c r="C31" t="n">
-        <v>-1.24</v>
+        <v>-1.2086</v>
       </c>
       <c r="D31" t="n">
-        <v>-2.273</v>
+        <v>-2.2311</v>
       </c>
       <c r="E31" t="n">
-        <v>-3.6216</v>
+        <v>-3.5299</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.6216</v>
+        <v>-2.5299</v>
       </c>
       <c r="G31" t="n">
         <v>-1</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.6216</v>
+        <v>-2.5299</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.6216</v>
+        <v>-2.5299</v>
       </c>
       <c r="J31" t="n">
         <v>-1</v>
@@ -1863,7 +1863,7 @@
         <v>68</v>
       </c>
       <c r="M31" t="n">
-        <v>-3.6216</v>
+        <v>-3.5299</v>
       </c>
       <c r="N31" t="n">
         <v>194</v>
@@ -1969,10 +1969,10 @@
         <v>1.32</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5809</v>
+        <v>0.5548</v>
       </c>
       <c r="J2" t="n">
-        <v>13.3607</v>
+        <v>12.7604</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>0.89</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.123</v>
+        <v>-0.1411</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.829</v>
+        <v>-3.2453</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>0.71</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3013</v>
+        <v>-0.3186</v>
       </c>
       <c r="J4" t="n">
-        <v>-6.9299</v>
+        <v>-7.3278</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4422</v>
+        <v>-0.4535</v>
       </c>
       <c r="J5" t="n">
-        <v>-10.1706</v>
+        <v>-10.4305</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.53</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.47</v>
+        <v>-0.4797</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.81</v>
+        <v>-11.0331</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.61</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7245</v>
+        <v>0.7216</v>
       </c>
       <c r="J7" t="n">
-        <v>16.6635</v>
+        <v>16.5968</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>1.48</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5868</v>
+        <v>0.5933</v>
       </c>
       <c r="J8" t="n">
-        <v>13.4964</v>
+        <v>13.6459</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>1.41</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5111</v>
+        <v>0.522</v>
       </c>
       <c r="J9" t="n">
-        <v>11.7553</v>
+        <v>12.006</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0264</v>
+        <v>-0.0204</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6072</v>
+        <v>-0.4692</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.91</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1516</v>
+        <v>-0.1577</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.4868</v>
+        <v>-3.6271</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>1.37</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9552</v>
+        <v>0.8963</v>
       </c>
       <c r="J12" t="n">
-        <v>23.88</v>
+        <v>22.4075</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.29</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7755</v>
+        <v>0.7361</v>
       </c>
       <c r="J13" t="n">
-        <v>19.3875</v>
+        <v>18.4025</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>1.21</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5866</v>
+        <v>0.5684</v>
       </c>
       <c r="J14" t="n">
-        <v>14.665</v>
+        <v>14.21</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>1.13</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3886</v>
+        <v>0.3885</v>
       </c>
       <c r="J15" t="n">
-        <v>9.715</v>
+        <v>9.7125</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.91</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3697</v>
+        <v>-0.35</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.2425</v>
+        <v>-8.75</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.4</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8538</v>
+        <v>0.8001</v>
       </c>
       <c r="J17" t="n">
-        <v>21.345</v>
+        <v>20.0025</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>1.09</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2651</v>
+        <v>0.2613</v>
       </c>
       <c r="J18" t="n">
-        <v>6.6275</v>
+        <v>6.5325</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>0.72</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3019</v>
+        <v>-0.3172</v>
       </c>
       <c r="J19" t="n">
-        <v>-7.5475</v>
+        <v>-7.93</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3306</v>
+        <v>-0.345</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.265000000000001</v>
+        <v>-8.625</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.48</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5249</v>
+        <v>-0.53</v>
       </c>
       <c r="J21" t="n">
-        <v>-13.1225</v>
+        <v>-13.25</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.94</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5937</v>
+        <v>1.7361</v>
       </c>
       <c r="J22" t="n">
-        <v>31.874</v>
+        <v>34.722</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.63</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2427</v>
+        <v>1.3016</v>
       </c>
       <c r="J23" t="n">
-        <v>24.854</v>
+        <v>26.032</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>1.42</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9414</v>
       </c>
       <c r="J24" t="n">
-        <v>19.728</v>
+        <v>18.828</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>1.37</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8891</v>
+        <v>0.8484</v>
       </c>
       <c r="J25" t="n">
-        <v>17.782</v>
+        <v>16.968</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>1.2</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4968</v>
+        <v>0.5014</v>
       </c>
       <c r="J26" t="n">
-        <v>9.936</v>
+        <v>10.028</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>0.75</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.2002</v>
+        <v>-0.2323</v>
       </c>
       <c r="J27" t="n">
-        <v>-4.004</v>
+        <v>-4.646</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>0.65</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3095</v>
+        <v>-0.3358</v>
       </c>
       <c r="J28" t="n">
-        <v>-6.19</v>
+        <v>-6.716</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>0.47</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4794</v>
+        <v>-0.4956</v>
       </c>
       <c r="J29" t="n">
-        <v>-9.587999999999999</v>
+        <v>-9.912000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>0.42</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.527</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.54</v>
+        <v>-10.796</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.37</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5756</v>
+        <v>-0.5845</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.512</v>
+        <v>-11.69</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.05</v>
       </c>
       <c r="I32" t="n">
-        <v>0.159</v>
+        <v>0.1621</v>
       </c>
       <c r="J32" t="n">
-        <v>4.77</v>
+        <v>4.863</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>0.96</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0568</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.704</v>
+        <v>-2.028</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>0.96</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0568</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.704</v>
+        <v>-2.028</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>0.84</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1891</v>
+        <v>-0.2048</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.673</v>
+        <v>-6.144</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>0.8</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2296</v>
+        <v>-0.2451</v>
       </c>
       <c r="J36" t="n">
-        <v>-6.888</v>
+        <v>-7.353</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.4</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7255</v>
+        <v>0.7054</v>
       </c>
       <c r="J37" t="n">
-        <v>21.765</v>
+        <v>21.162</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>1.24</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4651</v>
+        <v>0.4671</v>
       </c>
       <c r="J38" t="n">
-        <v>13.953</v>
+        <v>14.013</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>1.18</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3639</v>
+        <v>0.372</v>
       </c>
       <c r="J39" t="n">
-        <v>10.917</v>
+        <v>11.16</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>1.08</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1763</v>
+        <v>0.192</v>
       </c>
       <c r="J40" t="n">
-        <v>5.289</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.0168</v>
+        <v>-0.0129</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.504</v>
+        <v>-0.387</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.26</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7393</v>
+        <v>0.6979</v>
       </c>
       <c r="J42" t="n">
-        <v>22.179</v>
+        <v>20.937</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>1.19</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5649</v>
+        <v>0.5432</v>
       </c>
       <c r="J43" t="n">
-        <v>16.947</v>
+        <v>16.296</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>1.06</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2126</v>
+        <v>0.2193</v>
       </c>
       <c r="J44" t="n">
-        <v>6.378</v>
+        <v>6.579</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>0.97</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.15</v>
+        <v>-0.1492</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.5</v>
+        <v>-4.476</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>0.91</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3419</v>
+        <v>-0.3305</v>
       </c>
       <c r="J46" t="n">
-        <v>-10.257</v>
+        <v>-9.914999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>1.22</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4657</v>
+        <v>0.4605</v>
       </c>
       <c r="J47" t="n">
-        <v>13.971</v>
+        <v>13.815</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1.17</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3744</v>
+        <v>0.3756</v>
       </c>
       <c r="J48" t="n">
-        <v>11.232</v>
+        <v>11.268</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>1.02</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0626</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J49" t="n">
-        <v>1.878</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>0.89</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1486</v>
+        <v>-0.1608</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.458</v>
+        <v>-4.824</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.85</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1914</v>
+        <v>-0.2041</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.742</v>
+        <v>-6.123</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>2.23</v>
       </c>
       <c r="I52" t="n">
-        <v>1.8338</v>
+        <v>1.9067</v>
       </c>
       <c r="J52" t="n">
-        <v>33.0084</v>
+        <v>34.3206</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.71</v>
       </c>
       <c r="I53" t="n">
-        <v>1.322</v>
+        <v>1.3113</v>
       </c>
       <c r="J53" t="n">
-        <v>23.796</v>
+        <v>23.6034</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>1.49</v>
       </c>
       <c r="I54" t="n">
-        <v>1.0729</v>
+        <v>1.0404</v>
       </c>
       <c r="J54" t="n">
-        <v>19.3122</v>
+        <v>18.7272</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>1.44</v>
       </c>
       <c r="I55" t="n">
-        <v>1.0056</v>
+        <v>0.9635</v>
       </c>
       <c r="J55" t="n">
-        <v>18.1008</v>
+        <v>17.343</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>1.17</v>
       </c>
       <c r="I56" t="n">
-        <v>0.4029</v>
+        <v>0.4205</v>
       </c>
       <c r="J56" t="n">
-        <v>7.2522</v>
+        <v>7.569</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>0.87</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0648</v>
+        <v>-0.1003</v>
       </c>
       <c r="J57" t="n">
-        <v>-1.1664</v>
+        <v>-1.8054</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>0.66</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.3051</v>
+        <v>-0.3306</v>
       </c>
       <c r="J58" t="n">
-        <v>-5.4918</v>
+        <v>-5.9508</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>0.55</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.4104</v>
+        <v>-0.4303</v>
       </c>
       <c r="J59" t="n">
-        <v>-7.3872</v>
+        <v>-7.7454</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.4</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5502</v>
+        <v>-0.5606</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.903600000000001</v>
+        <v>-10.0908</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.27</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6775</v>
+        <v>-0.677</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.195</v>
+        <v>-12.186</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>1.35</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6945</v>
+        <v>0.6688</v>
       </c>
       <c r="J62" t="n">
-        <v>20.835</v>
+        <v>20.064</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>1.17</v>
       </c>
       <c r="I63" t="n">
-        <v>0.3766</v>
+        <v>0.3772</v>
       </c>
       <c r="J63" t="n">
-        <v>11.298</v>
+        <v>11.316</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>1.05</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1352</v>
+        <v>0.145</v>
       </c>
       <c r="J64" t="n">
-        <v>4.056</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>1.04</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1123</v>
+        <v>0.1219</v>
       </c>
       <c r="J65" t="n">
-        <v>3.369</v>
+        <v>3.657</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.5</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5213</v>
+        <v>-0.5245</v>
       </c>
       <c r="J66" t="n">
-        <v>-15.639</v>
+        <v>-15.735</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.44</v>
       </c>
       <c r="I67" t="n">
-        <v>1.0904</v>
+        <v>1.0427</v>
       </c>
       <c r="J67" t="n">
-        <v>32.712</v>
+        <v>31.281</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.16</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4819</v>
+        <v>0.4699</v>
       </c>
       <c r="J68" t="n">
-        <v>14.457</v>
+        <v>14.097</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>1.07</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2387</v>
+        <v>0.245</v>
       </c>
       <c r="J69" t="n">
-        <v>7.161</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>1.01</v>
       </c>
       <c r="I70" t="n">
-        <v>0.0323</v>
+        <v>0.0443</v>
       </c>
       <c r="J70" t="n">
-        <v>0.969</v>
+        <v>1.329</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6232</v>
+        <v>-0.584</v>
       </c>
       <c r="J71" t="n">
-        <v>-18.696</v>
+        <v>-17.52</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.14</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3145</v>
+        <v>0.3199</v>
       </c>
       <c r="J72" t="n">
-        <v>9.1205</v>
+        <v>9.277100000000001</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.1</v>
       </c>
       <c r="I73" t="n">
-        <v>0.2366</v>
+        <v>0.2454</v>
       </c>
       <c r="J73" t="n">
-        <v>6.8614</v>
+        <v>7.1166</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>1.03</v>
       </c>
       <c r="I74" t="n">
-        <v>0.0862</v>
+        <v>0.0961</v>
       </c>
       <c r="J74" t="n">
-        <v>2.4998</v>
+        <v>2.7869</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>0.98</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.04</v>
+        <v>-0.0458</v>
       </c>
       <c r="J75" t="n">
-        <v>-1.16</v>
+        <v>-1.3282</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>0.97</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.0543</v>
+        <v>-0.0614</v>
       </c>
       <c r="J76" t="n">
-        <v>-1.5747</v>
+        <v>-1.7806</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.24</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7239</v>
+        <v>0.6781</v>
       </c>
       <c r="J77" t="n">
-        <v>20.9931</v>
+        <v>19.6649</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>1.13</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4336</v>
+        <v>0.4193</v>
       </c>
       <c r="J78" t="n">
-        <v>12.5744</v>
+        <v>12.1597</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>1.12</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4057</v>
+        <v>0.394</v>
       </c>
       <c r="J79" t="n">
-        <v>11.7653</v>
+        <v>11.426</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.79</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.6471</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="J80" t="n">
-        <v>-18.7659</v>
+        <v>-17.7016</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.72</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.8243</v>
+        <v>-0.766</v>
       </c>
       <c r="J81" t="n">
-        <v>-23.9047</v>
+        <v>-22.214</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.72</v>
       </c>
       <c r="I82" t="n">
-        <v>1.4231</v>
+        <v>1.4025</v>
       </c>
       <c r="J82" t="n">
-        <v>32.7313</v>
+        <v>32.2575</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1.29</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7755</v>
+        <v>0.7361</v>
       </c>
       <c r="J83" t="n">
-        <v>17.8365</v>
+        <v>16.9303</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>1.24</v>
       </c>
       <c r="I84" t="n">
-        <v>0.6581</v>
+        <v>0.6323</v>
       </c>
       <c r="J84" t="n">
-        <v>15.1363</v>
+        <v>14.5429</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>0.83</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.5923</v>
+        <v>-0.5523</v>
       </c>
       <c r="J85" t="n">
-        <v>-13.6229</v>
+        <v>-12.7029</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.83</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5923</v>
+        <v>-0.5523</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.6229</v>
+        <v>-12.7029</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>0.98</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.0167</v>
+        <v>-0.0279</v>
       </c>
       <c r="J87" t="n">
-        <v>-0.3841</v>
+        <v>-0.6417</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>0.98</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0167</v>
+        <v>-0.0279</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.3841</v>
+        <v>-0.6417</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>0.88</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1402</v>
+        <v>-0.1572</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.2246</v>
+        <v>-3.6156</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.87</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1508</v>
+        <v>-0.1679</v>
       </c>
       <c r="J90" t="n">
-        <v>-3.4684</v>
+        <v>-3.8617</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.51</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4939</v>
+        <v>-0.5014</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.3597</v>
+        <v>-11.5322</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.5</v>
       </c>
       <c r="I92" t="n">
-        <v>1.1444</v>
+        <v>1.1069</v>
       </c>
       <c r="J92" t="n">
-        <v>29.7544</v>
+        <v>28.7794</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>1.45</v>
       </c>
       <c r="I93" t="n">
-        <v>1.0798</v>
+        <v>1.0354</v>
       </c>
       <c r="J93" t="n">
-        <v>28.0748</v>
+        <v>26.9204</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>1.36</v>
       </c>
       <c r="I94" t="n">
-        <v>0.9327</v>
+        <v>0.8752</v>
       </c>
       <c r="J94" t="n">
-        <v>24.2502</v>
+        <v>22.7552</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>0.85</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.5402</v>
+        <v>-0.5051</v>
       </c>
       <c r="J95" t="n">
-        <v>-14.0452</v>
+        <v>-13.1326</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.78</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.7235</v>
+        <v>-0.6688</v>
       </c>
       <c r="J96" t="n">
-        <v>-18.811</v>
+        <v>-17.3888</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.04</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1417</v>
+        <v>0.1432</v>
       </c>
       <c r="J97" t="n">
-        <v>3.6842</v>
+        <v>3.7232</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.0208</v>
+        <v>0.0149</v>
       </c>
       <c r="J98" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.3874</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>0.9</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1243</v>
+        <v>-0.1393</v>
       </c>
       <c r="J99" t="n">
-        <v>-3.2318</v>
+        <v>-3.6218</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>0.82</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2068</v>
+        <v>-0.2231</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.3768</v>
+        <v>-5.8006</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.74</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2858</v>
+        <v>-0.3009</v>
       </c>
       <c r="J101" t="n">
-        <v>-7.4308</v>
+        <v>-7.8234</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>1.53</v>
       </c>
       <c r="I102" t="n">
-        <v>1.1609</v>
+        <v>1.1286</v>
       </c>
       <c r="J102" t="n">
-        <v>31.3443</v>
+        <v>30.4722</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>1.39</v>
       </c>
       <c r="I103" t="n">
-        <v>0.9674</v>
+        <v>0.9135</v>
       </c>
       <c r="J103" t="n">
-        <v>26.1198</v>
+        <v>24.6645</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>1.31</v>
       </c>
       <c r="I104" t="n">
-        <v>0.7972</v>
+        <v>0.7599</v>
       </c>
       <c r="J104" t="n">
-        <v>21.5244</v>
+        <v>20.5173</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>1.27</v>
       </c>
       <c r="I105" t="n">
-        <v>0.7096</v>
+        <v>0.6819</v>
       </c>
       <c r="J105" t="n">
-        <v>19.1592</v>
+        <v>18.4113</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.91</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3939</v>
+        <v>-0.367</v>
       </c>
       <c r="J106" t="n">
-        <v>-10.6353</v>
+        <v>-9.909000000000001</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>0.9</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.1153</v>
+        <v>-0.1325</v>
       </c>
       <c r="J107" t="n">
-        <v>-3.1131</v>
+        <v>-3.5775</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>0.85</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.1692</v>
+        <v>-0.1871</v>
       </c>
       <c r="J108" t="n">
-        <v>-4.5684</v>
+        <v>-5.0517</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>0.85</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1692</v>
+        <v>-0.1871</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.5684</v>
+        <v>-5.0517</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>0.8</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2177</v>
+        <v>-0.2359</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.8779</v>
+        <v>-6.3693</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>0.72</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2948</v>
+        <v>-0.3117</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.9596</v>
+        <v>-8.415900000000001</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.17</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3697</v>
+        <v>0.3722</v>
       </c>
       <c r="J112" t="n">
-        <v>11.091</v>
+        <v>11.166</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>1.12</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2752</v>
+        <v>0.2826</v>
       </c>
       <c r="J113" t="n">
-        <v>8.256</v>
+        <v>8.478</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>1.07</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1745</v>
+        <v>0.1851</v>
       </c>
       <c r="J114" t="n">
-        <v>5.235</v>
+        <v>5.553</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>0.97</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.0547</v>
+        <v>-0.0618</v>
       </c>
       <c r="J115" t="n">
-        <v>-1.641</v>
+        <v>-1.854</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.91</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.1283</v>
+        <v>-0.1395</v>
       </c>
       <c r="J116" t="n">
-        <v>-3.849</v>
+        <v>-4.185</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.25</v>
       </c>
       <c r="I117" t="n">
-        <v>0.521</v>
+        <v>0.5111</v>
       </c>
       <c r="J117" t="n">
-        <v>15.63</v>
+        <v>15.333</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.07</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1786</v>
+        <v>0.188</v>
       </c>
       <c r="J118" t="n">
-        <v>5.358</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0016</v>
+        <v>-0.0012</v>
       </c>
       <c r="J119" t="n">
-        <v>-0.048</v>
+        <v>-0.036</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>0.93</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1026</v>
+        <v>-0.1135</v>
       </c>
       <c r="J120" t="n">
-        <v>-3.078</v>
+        <v>-3.405</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>0.87</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1696</v>
+        <v>-0.1823</v>
       </c>
       <c r="J121" t="n">
-        <v>-5.088</v>
+        <v>-5.469</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.51</v>
       </c>
       <c r="I122" t="n">
-        <v>1.1568</v>
+        <v>1.1202</v>
       </c>
       <c r="J122" t="n">
-        <v>28.92</v>
+        <v>28.005</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.35</v>
       </c>
       <c r="I123" t="n">
-        <v>0.9104</v>
+        <v>0.855</v>
       </c>
       <c r="J123" t="n">
-        <v>22.76</v>
+        <v>21.375</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>1.33</v>
       </c>
       <c r="I124" t="n">
-        <v>0.8653</v>
+        <v>0.8153</v>
       </c>
       <c r="J124" t="n">
-        <v>21.6325</v>
+        <v>20.3825</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>1.25</v>
       </c>
       <c r="I125" t="n">
-        <v>0.6798</v>
+        <v>0.652</v>
       </c>
       <c r="J125" t="n">
-        <v>16.995</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.51</v>
       </c>
       <c r="I126" t="n">
-        <v>-1.3655</v>
+        <v>-1.225</v>
       </c>
       <c r="J126" t="n">
-        <v>-34.1375</v>
+        <v>-30.625</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.29</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6523</v>
+        <v>0.6203</v>
       </c>
       <c r="J127" t="n">
-        <v>16.3075</v>
+        <v>15.5075</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1.07</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2178</v>
+        <v>0.2165</v>
       </c>
       <c r="J128" t="n">
-        <v>5.445</v>
+        <v>5.4125</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0892</v>
+        <v>-0.1033</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.23</v>
+        <v>-2.5825</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>0.68</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3411</v>
+        <v>-0.3549</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.5275</v>
+        <v>-8.8725</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.45</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5528</v>
+        <v>-0.5561</v>
       </c>
       <c r="J131" t="n">
-        <v>-13.82</v>
+        <v>-13.9025</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>1.35</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6833</v>
+        <v>0.6606</v>
       </c>
       <c r="J132" t="n">
-        <v>19.1324</v>
+        <v>18.4968</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1.03</v>
       </c>
       <c r="I133" t="n">
-        <v>0.0851</v>
+        <v>0.0953</v>
       </c>
       <c r="J133" t="n">
-        <v>2.3828</v>
+        <v>2.6684</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>1</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.0041</v>
+        <v>-0.0031</v>
       </c>
       <c r="J134" t="n">
-        <v>-0.1148</v>
+        <v>-0.0868</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>0.99</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0251</v>
+        <v>-0.0287</v>
       </c>
       <c r="J135" t="n">
-        <v>-0.7028</v>
+        <v>-0.8036</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.89</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.1511</v>
+        <v>-0.1627</v>
       </c>
       <c r="J136" t="n">
-        <v>-4.2308</v>
+        <v>-4.5556</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.25</v>
       </c>
       <c r="I137" t="n">
-        <v>0.7287</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="J137" t="n">
-        <v>20.4036</v>
+        <v>19.208</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>1.12</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3908</v>
+        <v>0.3836</v>
       </c>
       <c r="J138" t="n">
-        <v>10.9424</v>
+        <v>10.7408</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>1.07</v>
       </c>
       <c r="I139" t="n">
-        <v>0.248</v>
+        <v>0.2513</v>
       </c>
       <c r="J139" t="n">
-        <v>6.944</v>
+        <v>7.0364</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>0.92</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3025</v>
+        <v>-0.2963</v>
       </c>
       <c r="J140" t="n">
-        <v>-8.470000000000001</v>
+        <v>-8.2964</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.86</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4741</v>
+        <v>-0.4533</v>
       </c>
       <c r="J141" t="n">
-        <v>-13.2748</v>
+        <v>-12.6924</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.43</v>
       </c>
       <c r="I142" t="n">
-        <v>1.0375</v>
+        <v>0.9885</v>
       </c>
       <c r="J142" t="n">
-        <v>22.825</v>
+        <v>21.747</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>1.37</v>
       </c>
       <c r="I143" t="n">
-        <v>0.9333</v>
+        <v>0.8796</v>
       </c>
       <c r="J143" t="n">
-        <v>20.5326</v>
+        <v>19.3512</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>1.28</v>
       </c>
       <c r="I144" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.7034</v>
       </c>
       <c r="J144" t="n">
-        <v>16.1568</v>
+        <v>15.4748</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>1.21</v>
       </c>
       <c r="I145" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J145" t="n">
-        <v>12.6302</v>
+        <v>12.32</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>1.01</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0159</v>
       </c>
       <c r="J146" t="n">
-        <v>-0.1848</v>
+        <v>0.3498</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>0.87</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.1413</v>
+        <v>-0.1605</v>
       </c>
       <c r="J147" t="n">
-        <v>-3.1086</v>
+        <v>-3.531</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>0.86</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1522</v>
+        <v>-0.1715</v>
       </c>
       <c r="J148" t="n">
-        <v>-3.3484</v>
+        <v>-3.773</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>0.8</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2137</v>
+        <v>-0.2329</v>
       </c>
       <c r="J149" t="n">
-        <v>-4.7014</v>
+        <v>-5.1238</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>0.73</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2793</v>
+        <v>-0.2977</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.1446</v>
+        <v>-6.5494</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.64</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3643</v>
+        <v>-0.3798</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.0146</v>
+        <v>-8.355600000000001</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>1.65</v>
       </c>
       <c r="I152" t="n">
-        <v>1.3177</v>
+        <v>1.2944</v>
       </c>
       <c r="J152" t="n">
-        <v>36.8956</v>
+        <v>36.2432</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>1.48</v>
       </c>
       <c r="I153" t="n">
-        <v>1.1055</v>
+        <v>1.0673</v>
       </c>
       <c r="J153" t="n">
-        <v>30.954</v>
+        <v>29.8844</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>1.26</v>
       </c>
       <c r="I154" t="n">
-        <v>0.6916</v>
+        <v>0.6649</v>
       </c>
       <c r="J154" t="n">
-        <v>19.3648</v>
+        <v>18.6172</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.97</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1934</v>
+        <v>-0.1795</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.4152</v>
+        <v>-5.026</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.87</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4995</v>
+        <v>-0.4655</v>
       </c>
       <c r="J156" t="n">
-        <v>-13.986</v>
+        <v>-13.034</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>0.95</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.0505</v>
+        <v>-0.0665</v>
       </c>
       <c r="J157" t="n">
-        <v>-1.414</v>
+        <v>-1.862</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>0.91</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.1</v>
+        <v>-0.1177</v>
       </c>
       <c r="J158" t="n">
-        <v>-2.8</v>
+        <v>-3.2956</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>0.8</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2157</v>
+        <v>-0.2344</v>
       </c>
       <c r="J159" t="n">
-        <v>-6.0396</v>
+        <v>-6.5632</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>0.8</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2157</v>
+        <v>-0.2344</v>
       </c>
       <c r="J160" t="n">
-        <v>-6.0396</v>
+        <v>-6.5632</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>0.55</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4515</v>
+        <v>-0.4623</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.642</v>
+        <v>-12.9444</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.19</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4228</v>
+        <v>0.4185</v>
       </c>
       <c r="J162" t="n">
-        <v>12.684</v>
+        <v>12.555</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>1.17</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3854</v>
+        <v>0.3836</v>
       </c>
       <c r="J163" t="n">
-        <v>11.562</v>
+        <v>11.508</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>1</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0008</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="J164" t="n">
-        <v>0.024</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>0.89</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1444</v>
+        <v>-0.1575</v>
       </c>
       <c r="J165" t="n">
-        <v>-4.332</v>
+        <v>-4.725</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>0.71</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3258</v>
+        <v>-0.3377</v>
       </c>
       <c r="J166" t="n">
-        <v>-9.773999999999999</v>
+        <v>-10.131</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1.45</v>
       </c>
       <c r="I167" t="n">
-        <v>1.1032</v>
+        <v>1.0573</v>
       </c>
       <c r="J167" t="n">
-        <v>33.096</v>
+        <v>31.719</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>1.19</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5579</v>
+        <v>0.5384</v>
       </c>
       <c r="J168" t="n">
-        <v>16.737</v>
+        <v>16.152</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>1.09</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2958</v>
+        <v>0.2988</v>
       </c>
       <c r="J169" t="n">
-        <v>8.874000000000001</v>
+        <v>8.964</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>0.96</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1909</v>
+        <v>-0.1871</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.727</v>
+        <v>-5.613</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6237</v>
+        <v>-0.5844</v>
       </c>
       <c r="J171" t="n">
-        <v>-18.711</v>
+        <v>-17.532</v>
       </c>
     </row>
     <row r="172">
@@ -8769,10 +8769,10 @@
         <v>2.02</v>
       </c>
       <c r="I172" t="n">
-        <v>1.6794</v>
+        <v>1.6863</v>
       </c>
       <c r="J172" t="n">
-        <v>33.588</v>
+        <v>33.726</v>
       </c>
     </row>
     <row r="173">
@@ -8809,10 +8809,10 @@
         <v>1.89</v>
       </c>
       <c r="I173" t="n">
-        <v>1.5354</v>
+        <v>1.5352</v>
       </c>
       <c r="J173" t="n">
-        <v>30.708</v>
+        <v>30.704</v>
       </c>
     </row>
     <row r="174">
@@ -8849,10 +8849,10 @@
         <v>1.41</v>
       </c>
       <c r="I174" t="n">
-        <v>0.9669</v>
+        <v>0.921</v>
       </c>
       <c r="J174" t="n">
-        <v>19.338</v>
+        <v>18.42</v>
       </c>
     </row>
     <row r="175">
@@ -8889,10 +8889,10 @@
         <v>1.25</v>
       </c>
       <c r="I175" t="n">
-        <v>0.615</v>
+        <v>0.6073</v>
       </c>
       <c r="J175" t="n">
-        <v>12.3</v>
+        <v>12.146</v>
       </c>
     </row>
     <row r="176">
@@ -8929,10 +8929,10 @@
         <v>1.06</v>
       </c>
       <c r="I176" t="n">
-        <v>0.1123</v>
+        <v>0.1493</v>
       </c>
       <c r="J176" t="n">
-        <v>2.246</v>
+        <v>2.986</v>
       </c>
     </row>
     <row r="177">
@@ -8969,10 +8969,10 @@
         <v>0.96</v>
       </c>
       <c r="I177" t="n">
-        <v>0.1346</v>
+        <v>0.0603</v>
       </c>
       <c r="J177" t="n">
-        <v>2.692</v>
+        <v>1.206</v>
       </c>
     </row>
     <row r="178">
@@ -9009,10 +9009,10 @@
         <v>0.49</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.4603</v>
+        <v>-0.4779</v>
       </c>
       <c r="J178" t="n">
-        <v>-9.206</v>
+        <v>-9.558</v>
       </c>
     </row>
     <row r="179">
@@ -9049,10 +9049,10 @@
         <v>0.46</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.4884</v>
+        <v>-0.5041</v>
       </c>
       <c r="J179" t="n">
-        <v>-9.768000000000001</v>
+        <v>-10.082</v>
       </c>
     </row>
     <row r="180">
@@ -9089,10 +9089,10 @@
         <v>0.37</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.5752</v>
+        <v>-0.5841</v>
       </c>
       <c r="J180" t="n">
-        <v>-11.504</v>
+        <v>-11.682</v>
       </c>
     </row>
     <row r="181">
@@ -9129,10 +9129,10 @@
         <v>0.37</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5752</v>
+        <v>-0.5841</v>
       </c>
       <c r="J181" t="n">
-        <v>-11.504</v>
+        <v>-11.682</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4205/event_4205_evp_summary.xlsx
+++ b/database/event/4205/event_4205_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.5645</v>
+        <v>5.5254</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9052</v>
+        <v>1.8918</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9089</v>
+        <v>1.9113</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5645</v>
+        <v>5.5254</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5077</v>
+        <v>3.437</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0568</v>
+        <v>2.0884</v>
       </c>
       <c r="H2" t="n">
-        <v>4.9523</v>
+        <v>4.9265</v>
       </c>
       <c r="I2" t="n">
-        <v>5.2108</v>
+        <v>5.1933</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0568</v>
+        <v>2.0884</v>
       </c>
       <c r="K2" t="n">
         <v>125</v>
@@ -529,7 +529,7 @@
         <v>68</v>
       </c>
       <c r="M2" t="n">
-        <v>7.2676</v>
+        <v>7.2817</v>
       </c>
       <c r="N2" t="n">
         <v>193</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.3117</v>
+        <v>5.3534</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8187</v>
+        <v>1.8329</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7938</v>
+        <v>1.8329</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3117</v>
+        <v>5.3534</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3708</v>
+        <v>3.3024</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9409</v>
+        <v>2.051</v>
       </c>
       <c r="H3" t="n">
-        <v>4.6526</v>
+        <v>4.6179</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8955</v>
+        <v>4.868</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9409</v>
+        <v>2.051</v>
       </c>
       <c r="K3" t="n">
         <v>125</v>
@@ -575,7 +575,7 @@
         <v>68</v>
       </c>
       <c r="M3" t="n">
-        <v>6.8364</v>
+        <v>6.919</v>
       </c>
       <c r="N3" t="n">
         <v>193</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.3095</v>
+        <v>3.205</v>
       </c>
       <c r="C4" t="n">
-        <v>1.1331</v>
+        <v>1.0974</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8823</v>
+        <v>0.8542</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3095</v>
+        <v>3.205</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5589</v>
+        <v>2.5594</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7506</v>
+        <v>0.6456</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8758</v>
+        <v>2.9153</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8758</v>
+        <v>2.9153</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7506</v>
+        <v>0.6456</v>
       </c>
       <c r="K4" t="n">
         <v>126</v>
@@ -621,7 +621,7 @@
         <v>68</v>
       </c>
       <c r="M4" t="n">
-        <v>3.6264</v>
+        <v>3.5609</v>
       </c>
       <c r="N4" t="n">
         <v>194</v>
@@ -630,93 +630,93 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.9047</v>
+        <v>2.9125</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9945000000000001</v>
+        <v>0.9972</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.721</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9047</v>
+        <v>2.9125</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9047</v>
+        <v>1.6664</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1.2461</v>
       </c>
       <c r="H5" t="n">
-        <v>3.6326</v>
+        <v>1.6664</v>
       </c>
       <c r="I5" t="n">
-        <v>3.6326</v>
+        <v>1.7566</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1.2461</v>
       </c>
       <c r="K5" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M5" t="n">
-        <v>3.6326</v>
+        <v>3.0027</v>
       </c>
       <c r="N5" t="n">
-        <v>123</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.8893</v>
+        <v>2.8554</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9893</v>
+        <v>0.9777</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6911</v>
+        <v>0.695</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8893</v>
+        <v>2.8554</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6234</v>
+        <v>2.8554</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2659</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6234</v>
+        <v>3.5936</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7081</v>
+        <v>3.5936</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2659</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="L6" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.974</v>
+        <v>3.5936</v>
       </c>
       <c r="N6" t="n">
-        <v>193</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.4623</v>
+        <v>2.3306</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8431</v>
+        <v>0.798</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4967</v>
+        <v>0.4559</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4623</v>
+        <v>2.3306</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2224</v>
+        <v>2.1339</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2399</v>
+        <v>0.1967</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2224</v>
+        <v>2.1339</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2224</v>
+        <v>2.1339</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2399</v>
+        <v>0.1967</v>
       </c>
       <c r="K7" t="n">
         <v>126</v>
@@ -759,7 +759,7 @@
         <v>68</v>
       </c>
       <c r="M7" t="n">
-        <v>2.4623</v>
+        <v>2.3306</v>
       </c>
       <c r="N7" t="n">
         <v>194</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.9754</v>
+        <v>1.7944</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6764</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.275</v>
+        <v>0.2116</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9754</v>
+        <v>1.7944</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0629</v>
+        <v>0.9468</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.08749999999999999</v>
+        <v>0.8476</v>
       </c>
       <c r="H8" t="n">
-        <v>2.0629</v>
+        <v>0.9468</v>
       </c>
       <c r="I8" t="n">
-        <v>2.0629</v>
+        <v>0.9981</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.08749999999999999</v>
+        <v>0.8476</v>
       </c>
       <c r="K8" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L8" t="n">
         <v>68</v>
       </c>
       <c r="M8" t="n">
-        <v>1.9754</v>
+        <v>1.8457</v>
       </c>
       <c r="N8" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.8469</v>
+        <v>1.7798</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6324</v>
+        <v>0.6094000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2165</v>
+        <v>0.205</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8469</v>
+        <v>1.7798</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9705</v>
+        <v>1.9133</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8764</v>
+        <v>-0.1335</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9705</v>
+        <v>1.9133</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0212</v>
+        <v>1.9133</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8764</v>
+        <v>-0.1335</v>
       </c>
       <c r="K9" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L9" t="n">
         <v>68</v>
       </c>
       <c r="M9" t="n">
-        <v>1.8976</v>
+        <v>1.7798</v>
       </c>
       <c r="N9" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.8188</v>
+        <v>1.7588</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6227</v>
+        <v>0.6022</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2038</v>
+        <v>0.1954</v>
       </c>
       <c r="E10" t="n">
-        <v>1.8188</v>
+        <v>1.7588</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8188</v>
+        <v>1.7588</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8188</v>
+        <v>1.7588</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8188</v>
+        <v>1.7588</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.8188</v>
+        <v>1.7588</v>
       </c>
       <c r="N10" t="n">
         <v>144</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.5355</v>
+        <v>1.5184</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5256999999999999</v>
+        <v>0.5199</v>
       </c>
       <c r="D11" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0859</v>
       </c>
       <c r="E11" t="n">
-        <v>1.5355</v>
+        <v>1.5184</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5355</v>
+        <v>1.5184</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5355</v>
+        <v>1.5184</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5355</v>
+        <v>1.5184</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.5355</v>
+        <v>1.5184</v>
       </c>
       <c r="N11" t="n">
         <v>123</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.3864</v>
+        <v>1.3223</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4747</v>
+        <v>0.4527</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0069</v>
+        <v>-0.0034</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3864</v>
+        <v>1.3223</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3864</v>
+        <v>1.3223</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3864</v>
+        <v>1.3223</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3864</v>
+        <v>1.3223</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3864</v>
+        <v>1.3223</v>
       </c>
       <c r="N12" t="n">
-        <v>144</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.3493</v>
+        <v>1.2734</v>
       </c>
       <c r="C13" t="n">
-        <v>0.462</v>
+        <v>0.436</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.01</v>
+        <v>-0.0257</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3493</v>
+        <v>1.2734</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3493</v>
+        <v>1.2734</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3493</v>
+        <v>1.2734</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3493</v>
+        <v>1.2734</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3493</v>
+        <v>1.2734</v>
       </c>
       <c r="N13" t="n">
-        <v>123</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14">
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.1476</v>
+        <v>1.1859</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3929</v>
+        <v>0.406</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1018</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1476</v>
+        <v>1.1859</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1476</v>
+        <v>1.1859</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1476</v>
+        <v>1.1859</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1476</v>
+        <v>1.1859</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1476</v>
+        <v>1.1859</v>
       </c>
       <c r="N14" t="n">
         <v>123</v>
@@ -1090,185 +1090,185 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>refrezh</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.952</v>
+        <v>0.9463</v>
       </c>
       <c r="C15" t="n">
-        <v>0.326</v>
+        <v>0.324</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1908</v>
+        <v>-0.1747</v>
       </c>
       <c r="E15" t="n">
-        <v>0.952</v>
+        <v>0.9463</v>
       </c>
       <c r="F15" t="n">
-        <v>0.952</v>
+        <v>0.9463</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.952</v>
+        <v>0.9463</v>
       </c>
       <c r="I15" t="n">
-        <v>0.952</v>
+        <v>0.9463</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.952</v>
+        <v>0.9463</v>
       </c>
       <c r="N15" t="n">
-        <v>123</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>refrezh</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.8954</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3236</v>
+        <v>0.3066</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.194</v>
+        <v>-0.1979</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.8954</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.8954</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.8954</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.8954</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.8954</v>
       </c>
       <c r="N16" t="n">
-        <v>144</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6328</v>
+        <v>0.5596</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2167</v>
+        <v>0.1916</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3361</v>
+        <v>-0.3509</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6328</v>
+        <v>0.5596</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0427</v>
+        <v>0.5596</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5901</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0427</v>
+        <v>0.5596</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0449</v>
+        <v>0.5596</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5901</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="L17" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.635</v>
+        <v>0.5596</v>
       </c>
       <c r="N17" t="n">
-        <v>193</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5816</v>
+        <v>0.5193</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1991</v>
+        <v>0.1778</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3594</v>
+        <v>-0.3692</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5816</v>
+        <v>0.5193</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5816</v>
+        <v>-0.0105</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.5298</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5816</v>
+        <v>-0.0105</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5816</v>
+        <v>-0.0111</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.5298</v>
       </c>
       <c r="K18" t="n">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5816</v>
+        <v>0.5187</v>
       </c>
       <c r="N18" t="n">
-        <v>137</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.2896</v>
+        <v>0.2455</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0992</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4924</v>
+        <v>-0.494</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2896</v>
+        <v>0.2455</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2896</v>
+        <v>0.2455</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2896</v>
+        <v>0.2455</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2896</v>
+        <v>0.2455</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2896</v>
+        <v>0.2455</v>
       </c>
       <c r="N19" t="n">
         <v>137</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1832</v>
+        <v>0.131</v>
       </c>
       <c r="C20" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0449</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-0.5461</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1832</v>
+        <v>0.131</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1832</v>
+        <v>0.131</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1832</v>
+        <v>0.131</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1832</v>
+        <v>0.131</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1832</v>
+        <v>0.131</v>
       </c>
       <c r="N20" t="n">
         <v>144</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1333</v>
+        <v>0.064</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0456</v>
+        <v>0.0219</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5635</v>
+        <v>-0.5766</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1333</v>
+        <v>0.064</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1333</v>
+        <v>0.064</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1333</v>
+        <v>0.064</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1333</v>
+        <v>0.064</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1333</v>
+        <v>0.064</v>
       </c>
       <c r="N21" t="n">
         <v>137</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0258</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0251</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5908</v>
+        <v>-0.594</v>
       </c>
       <c r="E22" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0258</v>
       </c>
       <c r="F22" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0258</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0258</v>
       </c>
       <c r="I22" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0258</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0258</v>
       </c>
       <c r="N22" t="n">
         <v>137</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0461</v>
+        <v>-0.0774</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0158</v>
+        <v>-0.0265</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6032</v>
+        <v>-0.641</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0461</v>
+        <v>-0.0774</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0461</v>
+        <v>-0.0774</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0461</v>
+        <v>-0.0774</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0461</v>
+        <v>-0.0774</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0461</v>
+        <v>-0.0774</v>
       </c>
       <c r="N23" t="n">
         <v>137</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.0171</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0059</v>
+        <v>-0.0309</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.632</v>
+        <v>-0.6469</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0171</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0171</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0171</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0171</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0171</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="N24" t="n">
         <v>137</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1454</v>
+        <v>-0.1573</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0498</v>
+        <v>-0.0539</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6904</v>
+        <v>-0.6774</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1454</v>
+        <v>-0.1573</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1454</v>
+        <v>-0.1573</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1454</v>
+        <v>-0.1573</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1454</v>
+        <v>-0.1573</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1454</v>
+        <v>-0.1573</v>
       </c>
       <c r="N25" t="n">
         <v>137</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.6683</v>
+        <v>-0.6806</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.2288</v>
+        <v>-0.233</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.9284</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.6683</v>
+        <v>-0.6806</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6683</v>
+        <v>-0.6806</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.6683</v>
+        <v>-0.6806</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6683</v>
+        <v>-0.6806</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.6683</v>
+        <v>-0.6806</v>
       </c>
       <c r="N26" t="n">
         <v>137</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.8514</v>
+        <v>-0.8203</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.2915</v>
+        <v>-0.2809</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.0118</v>
+        <v>-0.9795</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.8514</v>
+        <v>-0.8203</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.8514</v>
+        <v>-0.8203</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.8514</v>
+        <v>-0.8203</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.8514</v>
+        <v>-0.8203</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.8514</v>
+        <v>-0.8203</v>
       </c>
       <c r="N27" t="n">
         <v>137</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.1005</v>
+        <v>-1.0899</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.3768</v>
+        <v>-0.3732</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.1252</v>
+        <v>-1.1023</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.1005</v>
+        <v>-1.0899</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.1005</v>
+        <v>-1.0899</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.1005</v>
+        <v>-1.0899</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.1005</v>
+        <v>-1.0899</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.1005</v>
+        <v>-1.0899</v>
       </c>
       <c r="N28" t="n">
         <v>137</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.3843</v>
+        <v>-1.3058</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.474</v>
+        <v>-0.4471</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.2544</v>
+        <v>-1.2006</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.3843</v>
+        <v>-1.3058</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.3843</v>
+        <v>-1.3058</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.3843</v>
+        <v>-1.3058</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.3843</v>
+        <v>-1.3058</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.3843</v>
+        <v>-1.3058</v>
       </c>
       <c r="N29" t="n">
         <v>144</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.8581</v>
+        <v>-2.8227</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.9786</v>
+        <v>-0.9665</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.9253</v>
+        <v>-1.8917</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.8581</v>
+        <v>-2.8227</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.5673</v>
+        <v>-2.4824</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.2908</v>
+        <v>-0.3403</v>
       </c>
       <c r="H30" t="n">
-        <v>-2.5673</v>
+        <v>-2.4824</v>
       </c>
       <c r="I30" t="n">
-        <v>-2.5673</v>
+        <v>-2.4824</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.2908</v>
+        <v>-0.3403</v>
       </c>
       <c r="K30" t="n">
         <v>126</v>
@@ -1817,7 +1817,7 @@
         <v>68</v>
       </c>
       <c r="M30" t="n">
-        <v>-2.8581</v>
+        <v>-2.8227</v>
       </c>
       <c r="N30" t="n">
         <v>194</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-3.5299</v>
+        <v>-3.4015</v>
       </c>
       <c r="C31" t="n">
-        <v>-1.2086</v>
+        <v>-1.1646</v>
       </c>
       <c r="D31" t="n">
-        <v>-2.2311</v>
+        <v>-2.1553</v>
       </c>
       <c r="E31" t="n">
-        <v>-3.5299</v>
+        <v>-3.4015</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.5299</v>
+        <v>-2.4015</v>
       </c>
       <c r="G31" t="n">
         <v>-1</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.5299</v>
+        <v>-2.4015</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.5299</v>
+        <v>-2.4015</v>
       </c>
       <c r="J31" t="n">
         <v>-1</v>
@@ -1863,7 +1863,7 @@
         <v>68</v>
       </c>
       <c r="M31" t="n">
-        <v>-3.5299</v>
+        <v>-3.4015</v>
       </c>
       <c r="N31" t="n">
         <v>194</v>
@@ -1969,10 +1969,10 @@
         <v>1.32</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5548</v>
+        <v>0.5888</v>
       </c>
       <c r="J2" t="n">
-        <v>12.7604</v>
+        <v>13.5424</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>0.89</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1411</v>
+        <v>-0.1256</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.2453</v>
+        <v>-2.8888</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>0.71</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3186</v>
+        <v>-0.3021</v>
       </c>
       <c r="J4" t="n">
-        <v>-7.3278</v>
+        <v>-6.9483</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4535</v>
+        <v>-0.4471</v>
       </c>
       <c r="J5" t="n">
-        <v>-10.4305</v>
+        <v>-10.2833</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.53</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4797</v>
+        <v>-0.4763</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.0331</v>
+        <v>-10.9549</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>1.61</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7216</v>
+        <v>0.6494</v>
       </c>
       <c r="J7" t="n">
-        <v>16.5968</v>
+        <v>14.9362</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>1.48</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5933</v>
+        <v>0.5229</v>
       </c>
       <c r="J8" t="n">
-        <v>13.6459</v>
+        <v>12.0267</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>1.41</v>
       </c>
       <c r="I9" t="n">
-        <v>0.522</v>
+        <v>0.4543</v>
       </c>
       <c r="J9" t="n">
-        <v>12.006</v>
+        <v>10.4489</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0204</v>
+        <v>-0.0181</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4692</v>
+        <v>-0.4163</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.91</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1577</v>
+        <v>-0.1393</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.6271</v>
+        <v>-3.2039</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>1.37</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8963</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>22.4075</v>
+        <v>21.9625</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>1.29</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7361</v>
+        <v>0.7074</v>
       </c>
       <c r="J13" t="n">
-        <v>18.4025</v>
+        <v>17.685</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>1.21</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5684</v>
+        <v>0.5337</v>
       </c>
       <c r="J14" t="n">
-        <v>14.21</v>
+        <v>13.3425</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>1.13</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3885</v>
+        <v>0.3535</v>
       </c>
       <c r="J15" t="n">
-        <v>9.7125</v>
+        <v>8.8375</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.91</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.35</v>
+        <v>-0.3089</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.75</v>
+        <v>-7.7225</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.4</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8001</v>
+        <v>0.7588</v>
       </c>
       <c r="J17" t="n">
-        <v>20.0025</v>
+        <v>18.97</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>1.09</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2613</v>
+        <v>0.215</v>
       </c>
       <c r="J18" t="n">
-        <v>6.5325</v>
+        <v>5.375</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>0.72</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3172</v>
+        <v>-0.3</v>
       </c>
       <c r="J19" t="n">
-        <v>-7.93</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.345</v>
+        <v>-0.3294</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.625</v>
+        <v>-8.234999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.48</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.53</v>
+        <v>-0.5343</v>
       </c>
       <c r="J21" t="n">
-        <v>-13.25</v>
+        <v>-13.3575</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.94</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7361</v>
+        <v>1.7711</v>
       </c>
       <c r="J22" t="n">
-        <v>34.722</v>
+        <v>35.422</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.63</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3016</v>
+        <v>1.3355</v>
       </c>
       <c r="J23" t="n">
-        <v>26.032</v>
+        <v>26.71</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>1.42</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9414</v>
+        <v>0.9412</v>
       </c>
       <c r="J24" t="n">
-        <v>18.828</v>
+        <v>18.824</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>1.37</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8484</v>
+        <v>0.8408</v>
       </c>
       <c r="J25" t="n">
-        <v>16.968</v>
+        <v>16.816</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>1.2</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5014</v>
+        <v>0.4724</v>
       </c>
       <c r="J26" t="n">
-        <v>10.028</v>
+        <v>9.448</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>0.75</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.2323</v>
+        <v>-0.2143</v>
       </c>
       <c r="J27" t="n">
-        <v>-4.646</v>
+        <v>-4.286</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>0.65</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3358</v>
+        <v>-0.327</v>
       </c>
       <c r="J28" t="n">
-        <v>-6.716</v>
+        <v>-6.54</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>0.47</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4956</v>
+        <v>-0.4946</v>
       </c>
       <c r="J29" t="n">
-        <v>-9.912000000000001</v>
+        <v>-9.891999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>0.42</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.5426</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.796</v>
+        <v>-10.852</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.37</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5845</v>
+        <v>-0.5928</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.69</v>
+        <v>-11.856</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.05</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1621</v>
+        <v>0.1253</v>
       </c>
       <c r="J32" t="n">
-        <v>4.863</v>
+        <v>3.759</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>0.96</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0555</v>
       </c>
       <c r="J33" t="n">
-        <v>-2.028</v>
+        <v>-1.665</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>0.96</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0555</v>
       </c>
       <c r="J34" t="n">
-        <v>-2.028</v>
+        <v>-1.665</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>0.84</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2048</v>
+        <v>-0.1847</v>
       </c>
       <c r="J35" t="n">
-        <v>-6.144</v>
+        <v>-5.541</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>0.8</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2451</v>
+        <v>-0.2252</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.353</v>
+        <v>-6.756</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.4</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7054</v>
+        <v>0.6471</v>
       </c>
       <c r="J37" t="n">
-        <v>21.162</v>
+        <v>19.413</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>1.24</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4671</v>
+        <v>0.4114</v>
       </c>
       <c r="J38" t="n">
-        <v>14.013</v>
+        <v>12.342</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>1.18</v>
       </c>
       <c r="I39" t="n">
-        <v>0.372</v>
+        <v>0.3214</v>
       </c>
       <c r="J39" t="n">
-        <v>11.16</v>
+        <v>9.641999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>1.08</v>
       </c>
       <c r="I40" t="n">
-        <v>0.192</v>
+        <v>0.1569</v>
       </c>
       <c r="J40" t="n">
-        <v>5.76</v>
+        <v>4.707</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.0129</v>
+        <v>-0.0104</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.387</v>
+        <v>-0.312</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.26</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6979</v>
+        <v>0.6643</v>
       </c>
       <c r="J42" t="n">
-        <v>20.937</v>
+        <v>19.929</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>1.19</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5432</v>
+        <v>0.5034</v>
       </c>
       <c r="J43" t="n">
-        <v>16.296</v>
+        <v>15.102</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>1.06</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2193</v>
+        <v>0.187</v>
       </c>
       <c r="J44" t="n">
-        <v>6.579</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>0.97</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1492</v>
+        <v>-0.1184</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.476</v>
+        <v>-3.552</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>0.91</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3305</v>
+        <v>-0.2884</v>
       </c>
       <c r="J46" t="n">
-        <v>-9.914999999999999</v>
+        <v>-8.651999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>1.22</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4605</v>
+        <v>0.4022</v>
       </c>
       <c r="J47" t="n">
-        <v>13.815</v>
+        <v>12.066</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1.17</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3756</v>
+        <v>0.3205</v>
       </c>
       <c r="J48" t="n">
-        <v>11.268</v>
+        <v>9.615</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>1.02</v>
       </c>
       <c r="I49" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0515</v>
       </c>
       <c r="J49" t="n">
-        <v>2.13</v>
+        <v>1.545</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>0.89</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1608</v>
+        <v>-0.1406</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.824</v>
+        <v>-4.218</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.85</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2041</v>
+        <v>-0.1835</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.123</v>
+        <v>-5.505</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>2.23</v>
       </c>
       <c r="I52" t="n">
-        <v>1.9067</v>
+        <v>1.9747</v>
       </c>
       <c r="J52" t="n">
-        <v>34.3206</v>
+        <v>35.5446</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.71</v>
       </c>
       <c r="I53" t="n">
-        <v>1.3113</v>
+        <v>1.3361</v>
       </c>
       <c r="J53" t="n">
-        <v>23.6034</v>
+        <v>24.0498</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>1.49</v>
       </c>
       <c r="I54" t="n">
-        <v>1.0404</v>
+        <v>1.0572</v>
       </c>
       <c r="J54" t="n">
-        <v>18.7272</v>
+        <v>19.0296</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>1.44</v>
       </c>
       <c r="I55" t="n">
-        <v>0.9635</v>
+        <v>0.9701</v>
       </c>
       <c r="J55" t="n">
-        <v>17.343</v>
+        <v>17.4618</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>1.17</v>
       </c>
       <c r="I56" t="n">
-        <v>0.4205</v>
+        <v>0.3874</v>
       </c>
       <c r="J56" t="n">
-        <v>7.569</v>
+        <v>6.9732</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>0.87</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.1003</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="J57" t="n">
-        <v>-1.8054</v>
+        <v>-1.2942</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>0.66</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.3306</v>
+        <v>-0.3215</v>
       </c>
       <c r="J58" t="n">
-        <v>-5.9508</v>
+        <v>-5.787</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>0.55</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.4303</v>
+        <v>-0.4256</v>
       </c>
       <c r="J59" t="n">
-        <v>-7.7454</v>
+        <v>-7.6608</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.4</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5606</v>
+        <v>-0.5658</v>
       </c>
       <c r="J60" t="n">
-        <v>-10.0908</v>
+        <v>-10.1844</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.27</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.677</v>
+        <v>-0.7015</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.186</v>
+        <v>-12.627</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>1.35</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6688</v>
+        <v>0.6108</v>
       </c>
       <c r="J62" t="n">
-        <v>20.064</v>
+        <v>18.324</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>1.17</v>
       </c>
       <c r="I63" t="n">
-        <v>0.3772</v>
+        <v>0.322</v>
       </c>
       <c r="J63" t="n">
-        <v>11.316</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>1.05</v>
       </c>
       <c r="I64" t="n">
-        <v>0.145</v>
+        <v>0.112</v>
       </c>
       <c r="J64" t="n">
-        <v>4.35</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>1.04</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1219</v>
+        <v>0.0926</v>
       </c>
       <c r="J65" t="n">
-        <v>3.657</v>
+        <v>2.778</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.5</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5245</v>
+        <v>-0.53</v>
       </c>
       <c r="J66" t="n">
-        <v>-15.735</v>
+        <v>-15.9</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.44</v>
       </c>
       <c r="I67" t="n">
-        <v>1.0427</v>
+        <v>1.0477</v>
       </c>
       <c r="J67" t="n">
-        <v>31.281</v>
+        <v>31.431</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.16</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4699</v>
+        <v>0.4299</v>
       </c>
       <c r="J68" t="n">
-        <v>14.097</v>
+        <v>12.897</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>1.07</v>
       </c>
       <c r="I69" t="n">
-        <v>0.245</v>
+        <v>0.2119</v>
       </c>
       <c r="J69" t="n">
-        <v>7.35</v>
+        <v>6.357</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>1.01</v>
       </c>
       <c r="I70" t="n">
-        <v>0.0443</v>
+        <v>0.0331</v>
       </c>
       <c r="J70" t="n">
-        <v>1.329</v>
+        <v>0.993</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.584</v>
+        <v>-0.5456</v>
       </c>
       <c r="J71" t="n">
-        <v>-17.52</v>
+        <v>-16.368</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.14</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3199</v>
+        <v>0.2685</v>
       </c>
       <c r="J72" t="n">
-        <v>9.277100000000001</v>
+        <v>7.7865</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>1.1</v>
       </c>
       <c r="I73" t="n">
-        <v>0.2454</v>
+        <v>0.2005</v>
       </c>
       <c r="J73" t="n">
-        <v>7.1166</v>
+        <v>5.8145</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>1.03</v>
       </c>
       <c r="I74" t="n">
-        <v>0.0961</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="J74" t="n">
-        <v>2.7869</v>
+        <v>2.088</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>0.98</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.0458</v>
+        <v>-0.0346</v>
       </c>
       <c r="J75" t="n">
-        <v>-1.3282</v>
+        <v>-1.0034</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>0.97</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.0614</v>
+        <v>-0.048</v>
       </c>
       <c r="J76" t="n">
-        <v>-1.7806</v>
+        <v>-1.392</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.24</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6781</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="J77" t="n">
-        <v>19.6649</v>
+        <v>18.6644</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>1.13</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4193</v>
+        <v>0.3764</v>
       </c>
       <c r="J78" t="n">
-        <v>12.1597</v>
+        <v>10.9156</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>1.12</v>
       </c>
       <c r="I79" t="n">
-        <v>0.394</v>
+        <v>0.3512</v>
       </c>
       <c r="J79" t="n">
-        <v>11.426</v>
+        <v>10.1848</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>0.79</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="J80" t="n">
-        <v>-17.7016</v>
+        <v>-16.5909</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.72</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.766</v>
+        <v>-0.7378</v>
       </c>
       <c r="J81" t="n">
-        <v>-22.214</v>
+        <v>-21.3962</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.72</v>
       </c>
       <c r="I82" t="n">
-        <v>1.4025</v>
+        <v>1.4308</v>
       </c>
       <c r="J82" t="n">
-        <v>32.2575</v>
+        <v>32.9084</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1.29</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7361</v>
+        <v>0.7074</v>
       </c>
       <c r="J83" t="n">
-        <v>16.9303</v>
+        <v>16.2702</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>1.24</v>
       </c>
       <c r="I84" t="n">
-        <v>0.6323</v>
+        <v>0.5991</v>
       </c>
       <c r="J84" t="n">
-        <v>14.5429</v>
+        <v>13.7793</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>0.83</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.5523</v>
+        <v>-0.5142</v>
       </c>
       <c r="J85" t="n">
-        <v>-12.7029</v>
+        <v>-11.8266</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.83</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5523</v>
+        <v>-0.5142</v>
       </c>
       <c r="J86" t="n">
-        <v>-12.7029</v>
+        <v>-11.8266</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>0.98</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.0279</v>
+        <v>-0.0207</v>
       </c>
       <c r="J87" t="n">
-        <v>-0.6417</v>
+        <v>-0.4761</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>0.98</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0279</v>
+        <v>-0.0207</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.6417</v>
+        <v>-0.4761</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>0.88</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1572</v>
+        <v>-0.1403</v>
       </c>
       <c r="J89" t="n">
-        <v>-3.6156</v>
+        <v>-3.2269</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.87</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1679</v>
+        <v>-0.1507</v>
       </c>
       <c r="J90" t="n">
-        <v>-3.8617</v>
+        <v>-3.4661</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.51</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5014</v>
+        <v>-0.5012</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.5322</v>
+        <v>-11.5276</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.5</v>
       </c>
       <c r="I92" t="n">
-        <v>1.1069</v>
+        <v>1.1185</v>
       </c>
       <c r="J92" t="n">
-        <v>28.7794</v>
+        <v>29.081</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>1.45</v>
       </c>
       <c r="I93" t="n">
-        <v>1.0354</v>
+        <v>1.0384</v>
       </c>
       <c r="J93" t="n">
-        <v>26.9204</v>
+        <v>26.9984</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>1.36</v>
       </c>
       <c r="I94" t="n">
-        <v>0.8752</v>
+        <v>0.8559</v>
       </c>
       <c r="J94" t="n">
-        <v>22.7552</v>
+        <v>22.2534</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>0.85</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.5051</v>
+        <v>-0.4656</v>
       </c>
       <c r="J95" t="n">
-        <v>-13.1326</v>
+        <v>-12.1056</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.78</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6688</v>
+        <v>-0.6374</v>
       </c>
       <c r="J96" t="n">
-        <v>-17.3888</v>
+        <v>-16.5724</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.04</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1432</v>
+        <v>0.1093</v>
       </c>
       <c r="J97" t="n">
-        <v>3.7232</v>
+        <v>2.8418</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.0149</v>
+        <v>0.0104</v>
       </c>
       <c r="J98" t="n">
-        <v>0.3874</v>
+        <v>0.2704</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>0.9</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1393</v>
+        <v>-0.1219</v>
       </c>
       <c r="J99" t="n">
-        <v>-3.6218</v>
+        <v>-3.1694</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>0.82</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2231</v>
+        <v>-0.2032</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.8006</v>
+        <v>-5.2832</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.74</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3009</v>
+        <v>-0.2828</v>
       </c>
       <c r="J101" t="n">
-        <v>-7.8234</v>
+        <v>-7.3528</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>1.53</v>
       </c>
       <c r="I102" t="n">
-        <v>1.1286</v>
+        <v>1.1414</v>
       </c>
       <c r="J102" t="n">
-        <v>30.4722</v>
+        <v>30.8178</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>1.39</v>
       </c>
       <c r="I103" t="n">
-        <v>0.9135</v>
+        <v>0.9005</v>
       </c>
       <c r="J103" t="n">
-        <v>24.6645</v>
+        <v>24.3135</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>1.31</v>
       </c>
       <c r="I104" t="n">
-        <v>0.7599</v>
+        <v>0.7371</v>
       </c>
       <c r="J104" t="n">
-        <v>20.5173</v>
+        <v>19.9017</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>1.27</v>
       </c>
       <c r="I105" t="n">
-        <v>0.6819</v>
+        <v>0.6556</v>
       </c>
       <c r="J105" t="n">
-        <v>18.4113</v>
+        <v>17.7012</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.91</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.367</v>
+        <v>-0.3282</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.909000000000001</v>
+        <v>-8.8614</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>0.9</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.1325</v>
+        <v>-0.117</v>
       </c>
       <c r="J107" t="n">
-        <v>-3.5775</v>
+        <v>-3.159</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>0.85</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.1871</v>
+        <v>-0.1698</v>
       </c>
       <c r="J108" t="n">
-        <v>-5.0517</v>
+        <v>-4.5846</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>0.85</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1871</v>
+        <v>-0.1698</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.0517</v>
+        <v>-4.5846</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>0.8</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2359</v>
+        <v>-0.2177</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.3693</v>
+        <v>-5.8779</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>0.72</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3117</v>
+        <v>-0.2946</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.415900000000001</v>
+        <v>-7.9542</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.17</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3722</v>
+        <v>0.3176</v>
       </c>
       <c r="J112" t="n">
-        <v>11.166</v>
+        <v>9.528</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>1.12</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2826</v>
+        <v>0.2344</v>
       </c>
       <c r="J113" t="n">
-        <v>8.478</v>
+        <v>7.032</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>1.07</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1851</v>
+        <v>0.1474</v>
       </c>
       <c r="J114" t="n">
-        <v>5.553</v>
+        <v>4.422</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>0.97</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.0618</v>
+        <v>-0.0483</v>
       </c>
       <c r="J115" t="n">
-        <v>-1.854</v>
+        <v>-1.449</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>0.91</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.1395</v>
+        <v>-0.1199</v>
       </c>
       <c r="J116" t="n">
-        <v>-4.185</v>
+        <v>-3.597</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>1.25</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5111</v>
+        <v>0.4518</v>
       </c>
       <c r="J117" t="n">
-        <v>15.333</v>
+        <v>13.554</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>1.07</v>
       </c>
       <c r="I118" t="n">
-        <v>0.188</v>
+        <v>0.1491</v>
       </c>
       <c r="J118" t="n">
-        <v>5.64</v>
+        <v>4.473</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0012</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="J119" t="n">
-        <v>-0.036</v>
+        <v>-0.018</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>0.93</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1135</v>
+        <v>-0.0954</v>
       </c>
       <c r="J120" t="n">
-        <v>-3.405</v>
+        <v>-2.862</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>0.87</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1823</v>
+        <v>-0.1617</v>
       </c>
       <c r="J121" t="n">
-        <v>-5.469</v>
+        <v>-4.851</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.51</v>
       </c>
       <c r="I122" t="n">
-        <v>1.1202</v>
+        <v>1.1324</v>
       </c>
       <c r="J122" t="n">
-        <v>28.005</v>
+        <v>28.31</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.35</v>
       </c>
       <c r="I123" t="n">
-        <v>0.855</v>
+        <v>0.8342000000000001</v>
       </c>
       <c r="J123" t="n">
-        <v>21.375</v>
+        <v>20.855</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>1.33</v>
       </c>
       <c r="I124" t="n">
-        <v>0.8153</v>
+        <v>0.7916</v>
       </c>
       <c r="J124" t="n">
-        <v>20.3825</v>
+        <v>19.79</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>1.25</v>
       </c>
       <c r="I125" t="n">
-        <v>0.652</v>
+        <v>0.6199</v>
       </c>
       <c r="J125" t="n">
-        <v>16.3</v>
+        <v>15.4975</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.51</v>
       </c>
       <c r="I126" t="n">
-        <v>-1.225</v>
+        <v>-1.2595</v>
       </c>
       <c r="J126" t="n">
-        <v>-30.625</v>
+        <v>-31.4875</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.29</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6203</v>
+        <v>0.5677</v>
       </c>
       <c r="J127" t="n">
-        <v>15.5075</v>
+        <v>14.1925</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1.07</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2165</v>
+        <v>0.1739</v>
       </c>
       <c r="J128" t="n">
-        <v>5.4125</v>
+        <v>4.3475</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1033</v>
+        <v>-0.0886</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.5825</v>
+        <v>-2.215</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>0.68</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3549</v>
+        <v>-0.3401</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.8725</v>
+        <v>-8.5025</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.45</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5561</v>
+        <v>-0.5645</v>
       </c>
       <c r="J131" t="n">
-        <v>-13.9025</v>
+        <v>-14.1125</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>1.35</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6606</v>
+        <v>0.6018</v>
       </c>
       <c r="J132" t="n">
-        <v>18.4968</v>
+        <v>16.8504</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>1.03</v>
       </c>
       <c r="I133" t="n">
-        <v>0.0953</v>
+        <v>0.0716</v>
       </c>
       <c r="J133" t="n">
-        <v>2.6684</v>
+        <v>2.0048</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>1</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.0031</v>
+        <v>-0.0019</v>
       </c>
       <c r="J134" t="n">
-        <v>-0.0868</v>
+        <v>-0.0532</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>0.99</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0287</v>
+        <v>-0.0204</v>
       </c>
       <c r="J135" t="n">
-        <v>-0.8036</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.89</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.1627</v>
+        <v>-0.1424</v>
       </c>
       <c r="J136" t="n">
-        <v>-4.5556</v>
+        <v>-3.9872</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.25</v>
       </c>
       <c r="I137" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6515</v>
       </c>
       <c r="J137" t="n">
-        <v>19.208</v>
+        <v>18.242</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>1.12</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3836</v>
+        <v>0.3422</v>
       </c>
       <c r="J138" t="n">
-        <v>10.7408</v>
+        <v>9.5816</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>1.07</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2513</v>
+        <v>0.215</v>
       </c>
       <c r="J139" t="n">
-        <v>7.0364</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>0.92</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2963</v>
+        <v>-0.2553</v>
       </c>
       <c r="J140" t="n">
-        <v>-8.2964</v>
+        <v>-7.1484</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.86</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4533</v>
+        <v>-0.4104</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.6924</v>
+        <v>-11.4912</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.43</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9885</v>
+        <v>0.9848</v>
       </c>
       <c r="J142" t="n">
-        <v>21.747</v>
+        <v>21.6656</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>1.37</v>
       </c>
       <c r="I143" t="n">
-        <v>0.8796</v>
+        <v>0.8629</v>
       </c>
       <c r="J143" t="n">
-        <v>19.3512</v>
+        <v>18.9838</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>1.28</v>
       </c>
       <c r="I144" t="n">
-        <v>0.7034</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="J144" t="n">
-        <v>15.4748</v>
+        <v>14.8918</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>1.21</v>
       </c>
       <c r="I145" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5291</v>
       </c>
       <c r="J145" t="n">
-        <v>12.32</v>
+        <v>11.6402</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>1.01</v>
       </c>
       <c r="I146" t="n">
-        <v>0.0159</v>
+        <v>0.0058</v>
       </c>
       <c r="J146" t="n">
-        <v>0.3498</v>
+        <v>0.1276</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>0.87</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.1605</v>
+        <v>-0.1448</v>
       </c>
       <c r="J147" t="n">
-        <v>-3.531</v>
+        <v>-3.1856</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>0.86</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1715</v>
+        <v>-0.1555</v>
       </c>
       <c r="J148" t="n">
-        <v>-3.773</v>
+        <v>-3.421</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>0.8</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2329</v>
+        <v>-0.2162</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.1238</v>
+        <v>-4.7564</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>0.73</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2977</v>
+        <v>-0.2811</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.5494</v>
+        <v>-6.1842</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>0.64</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3798</v>
+        <v>-0.3668</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.355600000000001</v>
+        <v>-8.069599999999999</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>1.65</v>
       </c>
       <c r="I152" t="n">
-        <v>1.2944</v>
+        <v>1.3137</v>
       </c>
       <c r="J152" t="n">
-        <v>36.2432</v>
+        <v>36.7836</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>1.48</v>
       </c>
       <c r="I153" t="n">
-        <v>1.0673</v>
+        <v>1.0756</v>
       </c>
       <c r="J153" t="n">
-        <v>29.8844</v>
+        <v>30.1168</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>1.26</v>
       </c>
       <c r="I154" t="n">
-        <v>0.6649</v>
+        <v>0.6362</v>
       </c>
       <c r="J154" t="n">
-        <v>18.6172</v>
+        <v>17.8136</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.97</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1795</v>
+        <v>-0.1487</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.026</v>
+        <v>-4.1636</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.87</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4655</v>
+        <v>-0.4263</v>
       </c>
       <c r="J156" t="n">
-        <v>-13.034</v>
+        <v>-11.9364</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>0.95</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.0665</v>
+        <v>-0.0546</v>
       </c>
       <c r="J157" t="n">
-        <v>-1.862</v>
+        <v>-1.5288</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>0.91</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.1177</v>
+        <v>-0.1031</v>
       </c>
       <c r="J158" t="n">
-        <v>-3.2956</v>
+        <v>-2.8868</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>0.8</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2344</v>
+        <v>-0.2169</v>
       </c>
       <c r="J159" t="n">
-        <v>-6.5632</v>
+        <v>-6.0732</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>0.8</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2344</v>
+        <v>-0.2169</v>
       </c>
       <c r="J160" t="n">
-        <v>-6.5632</v>
+        <v>-6.0732</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>0.55</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4623</v>
+        <v>-0.4568</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.9444</v>
+        <v>-12.7904</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.19</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4185</v>
+        <v>0.3614</v>
       </c>
       <c r="J162" t="n">
-        <v>12.555</v>
+        <v>10.842</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>1.17</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3836</v>
+        <v>0.328</v>
       </c>
       <c r="J163" t="n">
-        <v>11.508</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>1</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0002</v>
       </c>
       <c r="J164" t="n">
-        <v>0.018</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>0.89</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1575</v>
+        <v>-0.1376</v>
       </c>
       <c r="J165" t="n">
-        <v>-4.725</v>
+        <v>-4.128</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>0.71</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3377</v>
+        <v>-0.3221</v>
       </c>
       <c r="J166" t="n">
-        <v>-10.131</v>
+        <v>-9.663</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>1.45</v>
       </c>
       <c r="I167" t="n">
-        <v>1.0573</v>
+        <v>1.0647</v>
       </c>
       <c r="J167" t="n">
-        <v>31.719</v>
+        <v>31.941</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>1.19</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5384</v>
+        <v>0.4992</v>
       </c>
       <c r="J168" t="n">
-        <v>16.152</v>
+        <v>14.976</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>1.09</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2988</v>
+        <v>0.2628</v>
       </c>
       <c r="J169" t="n">
-        <v>8.964</v>
+        <v>7.884</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>0.96</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1871</v>
+        <v>-0.1526</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.613</v>
+        <v>-4.578</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5844</v>
+        <v>-0.546</v>
       </c>
       <c r="J171" t="n">
-        <v>-17.532</v>
+        <v>-16.38</v>
       </c>
     </row>
     <row r="172">
@@ -8769,10 +8769,10 @@
         <v>2.02</v>
       </c>
       <c r="I172" t="n">
-        <v>1.6863</v>
+        <v>1.7326</v>
       </c>
       <c r="J172" t="n">
-        <v>33.726</v>
+        <v>34.652</v>
       </c>
     </row>
     <row r="173">
@@ -8809,10 +8809,10 @@
         <v>1.89</v>
       </c>
       <c r="I173" t="n">
-        <v>1.5352</v>
+        <v>1.5695</v>
       </c>
       <c r="J173" t="n">
-        <v>30.704</v>
+        <v>31.39</v>
       </c>
     </row>
     <row r="174">
@@ -8849,10 +8849,10 @@
         <v>1.41</v>
       </c>
       <c r="I174" t="n">
-        <v>0.921</v>
+        <v>0.92</v>
       </c>
       <c r="J174" t="n">
-        <v>18.42</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="175">
@@ -8889,10 +8889,10 @@
         <v>1.25</v>
       </c>
       <c r="I175" t="n">
-        <v>0.6073</v>
+        <v>0.5836</v>
       </c>
       <c r="J175" t="n">
-        <v>12.146</v>
+        <v>11.672</v>
       </c>
     </row>
     <row r="176">
@@ -8929,10 +8929,10 @@
         <v>1.06</v>
       </c>
       <c r="I176" t="n">
-        <v>0.1493</v>
+        <v>0.1174</v>
       </c>
       <c r="J176" t="n">
-        <v>2.986</v>
+        <v>2.348</v>
       </c>
     </row>
     <row r="177">
@@ -8969,10 +8969,10 @@
         <v>0.96</v>
       </c>
       <c r="I177" t="n">
-        <v>0.0603</v>
+        <v>0.1218</v>
       </c>
       <c r="J177" t="n">
-        <v>1.206</v>
+        <v>2.436</v>
       </c>
     </row>
     <row r="178">
@@ -9009,10 +9009,10 @@
         <v>0.49</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.4779</v>
+        <v>-0.4759</v>
       </c>
       <c r="J178" t="n">
-        <v>-9.558</v>
+        <v>-9.518000000000001</v>
       </c>
     </row>
     <row r="179">
@@ -9049,10 +9049,10 @@
         <v>0.46</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.5041</v>
+        <v>-0.5036</v>
       </c>
       <c r="J179" t="n">
-        <v>-10.082</v>
+        <v>-10.072</v>
       </c>
     </row>
     <row r="180">
@@ -9089,10 +9089,10 @@
         <v>0.37</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.5841</v>
+        <v>-0.5924</v>
       </c>
       <c r="J180" t="n">
-        <v>-11.682</v>
+        <v>-11.848</v>
       </c>
     </row>
     <row r="181">
@@ -9129,10 +9129,10 @@
         <v>0.37</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5841</v>
+        <v>-0.5924</v>
       </c>
       <c r="J181" t="n">
-        <v>-11.682</v>
+        <v>-11.848</v>
       </c>
     </row>
   </sheetData>
